--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127154126</v>
+        <v>127153844</v>
       </c>
       <c r="B2" t="n">
-        <v>98382</v>
+        <v>80142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,35 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466247</v>
+        <v>466359</v>
       </c>
       <c r="R2" t="n">
-        <v>6809203</v>
+        <v>6809211</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127153844</v>
+        <v>127154126</v>
       </c>
       <c r="B3" t="n">
-        <v>80111</v>
+        <v>98457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,26 +787,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466359</v>
+        <v>466247</v>
       </c>
       <c r="R3" t="n">
-        <v>6809211</v>
+        <v>6809203</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127155482</v>
+        <v>127153831</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,21 +897,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -919,13 +919,8 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466081</v>
+        <v>466371</v>
       </c>
       <c r="R4" t="n">
-        <v>6809216</v>
+        <v>6809222</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,6 +972,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -995,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127153831</v>
+        <v>127155482</v>
       </c>
       <c r="B5" t="n">
-        <v>79012</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1028,8 +1024,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466371</v>
+        <v>466081</v>
       </c>
       <c r="R5" t="n">
-        <v>6809222</v>
+        <v>6809216</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1082,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127153848</v>
+        <v>127153643</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,37 +1111,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466359</v>
+        <v>466439</v>
       </c>
       <c r="R6" t="n">
-        <v>6809211</v>
+        <v>6809218</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1187,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1201,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127153643</v>
+        <v>127153848</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,42 +1216,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466439</v>
+        <v>466359</v>
       </c>
       <c r="R7" t="n">
-        <v>6809218</v>
+        <v>6809211</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,6 +1287,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154595</v>
+        <v>127155380</v>
       </c>
       <c r="B8" t="n">
         <v>57657</v>
@@ -1336,14 +1336,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466128</v>
+        <v>466021</v>
       </c>
       <c r="R8" t="n">
-        <v>6809202</v>
+        <v>6809226</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127155380</v>
+        <v>127154595</v>
       </c>
       <c r="B10" t="n">
         <v>57657</v>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466021</v>
+        <v>466128</v>
       </c>
       <c r="R10" t="n">
-        <v>6809226</v>
+        <v>6809202</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,17 +1626,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153712</v>
+        <v>127153532</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,14 +1667,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466164</v>
+        <v>466439</v>
       </c>
       <c r="R11" t="n">
-        <v>6809202</v>
+        <v>6809218</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,11 +1709,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1727,58 +1722,49 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153879</v>
+        <v>127153712</v>
       </c>
       <c r="B12" t="n">
-        <v>98382</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1786,10 +1772,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466321</v>
+        <v>466164</v>
       </c>
       <c r="R12" t="n">
-        <v>6809223</v>
+        <v>6809202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,6 +1810,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1837,60 +1828,69 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153532</v>
+        <v>127153879</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>98457</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466439</v>
+        <v>466321</v>
       </c>
       <c r="R13" t="n">
-        <v>6809218</v>
+        <v>6809223</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,7 +1953,7 @@
         <v>127154092</v>
       </c>
       <c r="B14" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127153742</v>
+        <v>127155565</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466410</v>
+        <v>466242</v>
       </c>
       <c r="R15" t="n">
-        <v>6809205</v>
+        <v>6809226</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127155565</v>
+        <v>127153742</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466242</v>
+        <v>466410</v>
       </c>
       <c r="R16" t="n">
-        <v>6809226</v>
+        <v>6809205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
         <v>127155475</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>127154066</v>
       </c>
       <c r="B18" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2575,45 +2575,53 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127154181</v>
+        <v>127153709</v>
       </c>
       <c r="B20" t="n">
-        <v>98278</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2621,10 +2629,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466206</v>
+        <v>466410</v>
       </c>
       <c r="R20" t="n">
-        <v>6809201</v>
+        <v>6809209</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,13 +2667,17 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2684,46 +2696,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127153709</v>
+        <v>127154181</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>98353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2731,10 +2735,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466410</v>
+        <v>466206</v>
       </c>
       <c r="R21" t="n">
-        <v>6809209</v>
+        <v>6809201</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,17 +2773,13 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2798,27 +2798,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127155506</v>
+        <v>127155499</v>
       </c>
       <c r="B22" t="n">
-        <v>5196</v>
+        <v>57654</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2826,13 +2826,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2886,7 +2889,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2905,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127155499</v>
+        <v>127153899</v>
       </c>
       <c r="B23" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2916,16 +2918,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2933,11 +2935,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
@@ -2952,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466085</v>
+        <v>466299</v>
       </c>
       <c r="R23" t="n">
-        <v>6809224</v>
+        <v>6809206</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,27 +3012,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127153899</v>
+        <v>127155506</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>5196</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3043,11 +3041,12 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3057,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466299</v>
+        <v>466085</v>
       </c>
       <c r="R24" t="n">
-        <v>6809206</v>
+        <v>6809224</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3101,6 +3100,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>127154177</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>127153768</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3326,10 +3326,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127153920</v>
+        <v>127154119</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466298</v>
+        <v>466247</v>
       </c>
       <c r="R27" t="n">
-        <v>6809205</v>
+        <v>6809203</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3427,10 +3427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127154119</v>
+        <v>127153920</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466247</v>
+        <v>466298</v>
       </c>
       <c r="R28" t="n">
-        <v>6809203</v>
+        <v>6809205</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,7 +3531,7 @@
         <v>127153894</v>
       </c>
       <c r="B29" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127154630</v>
+        <v>127154111</v>
       </c>
       <c r="B31" t="n">
-        <v>56849</v>
+        <v>57657</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3784,7 +3784,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466148</v>
+        <v>466259</v>
       </c>
       <c r="R31" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127154111</v>
+        <v>127155460</v>
       </c>
       <c r="B32" t="n">
         <v>57657</v>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466259</v>
+        <v>466067</v>
       </c>
       <c r="R32" t="n">
-        <v>6809208</v>
+        <v>6809228</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127155460</v>
+        <v>127154630</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>56849</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466067</v>
+        <v>466148</v>
       </c>
       <c r="R33" t="n">
-        <v>6809228</v>
+        <v>6809222</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4067,17 +4067,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127153911</v>
+        <v>127153408</v>
       </c>
       <c r="B34" t="n">
-        <v>97239</v>
+        <v>5176</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,38 +4085,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466299</v>
+        <v>466439</v>
       </c>
       <c r="R34" t="n">
-        <v>6809206</v>
+        <v>6809218</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4176,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127153408</v>
+        <v>127153911</v>
       </c>
       <c r="B35" t="n">
-        <v>5176</v>
+        <v>97314</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,43 +4192,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466439</v>
+        <v>466299</v>
       </c>
       <c r="R35" t="n">
-        <v>6809218</v>
+        <v>6809206</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153754</v>
+        <v>127153801</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,35 +4294,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4330,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466399</v>
+        <v>466383</v>
       </c>
       <c r="R36" t="n">
-        <v>6809202</v>
+        <v>6809213</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,6 +4365,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4392,10 +4384,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153801</v>
+        <v>127153754</v>
       </c>
       <c r="B37" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4403,26 +4395,35 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4430,10 +4431,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466383</v>
+        <v>466399</v>
       </c>
       <c r="R37" t="n">
-        <v>6809213</v>
+        <v>6809202</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,7 +4475,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127155517</v>
+        <v>127153599</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,37 +4504,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466108</v>
+        <v>466439</v>
       </c>
       <c r="R38" t="n">
-        <v>6809230</v>
+        <v>6809218</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4594,10 +4598,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127153599</v>
+        <v>127153858</v>
       </c>
       <c r="B39" t="n">
-        <v>79012</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4605,41 +4609,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466439</v>
+        <v>466333</v>
       </c>
       <c r="R39" t="n">
-        <v>6809218</v>
+        <v>6809211</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127153858</v>
+        <v>127155517</v>
       </c>
       <c r="B40" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4737,10 +4737,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466333</v>
+        <v>466108</v>
       </c>
       <c r="R40" t="n">
-        <v>6809211</v>
+        <v>6809230</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4800,44 +4800,36 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127154614</v>
+        <v>127153795</v>
       </c>
       <c r="B41" t="n">
-        <v>80049</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4846,10 +4838,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466148</v>
+        <v>466388</v>
       </c>
       <c r="R41" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4882,11 +4874,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4914,36 +4901,44 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127153795</v>
+        <v>127154614</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>80080</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4952,10 +4947,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466388</v>
+        <v>466148</v>
       </c>
       <c r="R42" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4988,6 +4983,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5015,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127153697</v>
+        <v>127153812</v>
       </c>
       <c r="B43" t="n">
-        <v>91263</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5026,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466269</v>
+        <v>466380</v>
       </c>
       <c r="R43" t="n">
-        <v>6809223</v>
+        <v>6809217</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,11 +5091,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5109,22 +5104,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127153812</v>
+        <v>127155443</v>
       </c>
       <c r="B44" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5159,10 +5154,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466380</v>
+        <v>466062</v>
       </c>
       <c r="R44" t="n">
-        <v>6809217</v>
+        <v>6809234</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5222,10 +5217,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127155443</v>
+        <v>127153697</v>
       </c>
       <c r="B45" t="n">
-        <v>78980</v>
+        <v>91337</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5233,21 +5228,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5260,10 +5255,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466062</v>
+        <v>466269</v>
       </c>
       <c r="R45" t="n">
-        <v>6809234</v>
+        <v>6809223</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5298,6 +5293,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5311,12 +5311,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127153844</v>
       </c>
       <c r="B2" t="n">
-        <v>80142</v>
+        <v>80145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127154126</v>
       </c>
       <c r="B3" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>127153831</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127153643</v>
+        <v>127153848</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,42 +1111,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466439</v>
+        <v>466359</v>
       </c>
       <c r="R6" t="n">
-        <v>6809218</v>
+        <v>6809211</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,6 +1182,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1205,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127153848</v>
+        <v>127153643</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,37 +1212,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466359</v>
+        <v>466439</v>
       </c>
       <c r="R7" t="n">
-        <v>6809211</v>
+        <v>6809218</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1288,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1626,17 +1626,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153532</v>
+        <v>127153712</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,14 +1667,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466439</v>
+        <v>466164</v>
       </c>
       <c r="R11" t="n">
-        <v>6809218</v>
+        <v>6809202</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1709,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1722,22 +1727,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153712</v>
+        <v>127153532</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1768,14 +1773,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466164</v>
+        <v>466439</v>
       </c>
       <c r="R12" t="n">
-        <v>6809202</v>
+        <v>6809218</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,11 +1815,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1828,12 +1828,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1843,7 +1843,7 @@
         <v>127153879</v>
       </c>
       <c r="B13" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>127154092</v>
       </c>
       <c r="B14" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155565</v>
+        <v>127155475</v>
       </c>
       <c r="B15" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466242</v>
+        <v>466076</v>
       </c>
       <c r="R15" t="n">
-        <v>6809226</v>
+        <v>6809225</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127153742</v>
+        <v>127155565</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466410</v>
+        <v>466242</v>
       </c>
       <c r="R16" t="n">
-        <v>6809205</v>
+        <v>6809226</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127155475</v>
+        <v>127153742</v>
       </c>
       <c r="B17" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466076</v>
+        <v>466410</v>
       </c>
       <c r="R17" t="n">
-        <v>6809225</v>
+        <v>6809205</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2363,46 +2363,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127154066</v>
+        <v>127154600</v>
       </c>
       <c r="B18" t="n">
-        <v>98457</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466274</v>
+        <v>466144</v>
       </c>
       <c r="R18" t="n">
-        <v>6809202</v>
+        <v>6809220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,7 +2454,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2473,46 +2472,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127154600</v>
+        <v>127154066</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>98463</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2520,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466144</v>
+        <v>466274</v>
       </c>
       <c r="R19" t="n">
-        <v>6809220</v>
+        <v>6809202</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,6 +2563,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2699,7 +2699,7 @@
         <v>127154181</v>
       </c>
       <c r="B21" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127154177</v>
+        <v>127154119</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466206</v>
+        <v>466247</v>
       </c>
       <c r="R25" t="n">
-        <v>6809201</v>
+        <v>6809203</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,10 +3220,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127153768</v>
+        <v>127154177</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466392</v>
+        <v>466206</v>
       </c>
       <c r="R26" t="n">
-        <v>6809204</v>
+        <v>6809201</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,11 +3294,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3326,10 +3321,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127154119</v>
+        <v>127153768</v>
       </c>
       <c r="B27" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466247</v>
+        <v>466392</v>
       </c>
       <c r="R27" t="n">
-        <v>6809203</v>
+        <v>6809204</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3400,6 +3395,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3430,7 +3430,7 @@
         <v>127153920</v>
       </c>
       <c r="B28" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3528,46 +3528,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127153894</v>
+        <v>127154103</v>
       </c>
       <c r="B29" t="n">
-        <v>98457</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466299</v>
+        <v>466254</v>
       </c>
       <c r="R29" t="n">
-        <v>6809206</v>
+        <v>6809208</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3619,7 +3619,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3638,46 +3637,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127154103</v>
+        <v>127153894</v>
       </c>
       <c r="B30" t="n">
-        <v>57657</v>
+        <v>98463</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3685,10 +3684,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466254</v>
+        <v>466299</v>
       </c>
       <c r="R30" t="n">
-        <v>6809208</v>
+        <v>6809206</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3729,6 +3728,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127154111</v>
+        <v>127154630</v>
       </c>
       <c r="B31" t="n">
-        <v>57657</v>
+        <v>56849</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3784,7 +3784,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466259</v>
+        <v>466148</v>
       </c>
       <c r="R31" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127155460</v>
+        <v>127154111</v>
       </c>
       <c r="B32" t="n">
         <v>57657</v>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466067</v>
+        <v>466259</v>
       </c>
       <c r="R32" t="n">
-        <v>6809228</v>
+        <v>6809208</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127154630</v>
+        <v>127155460</v>
       </c>
       <c r="B33" t="n">
-        <v>56849</v>
+        <v>57657</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466148</v>
+        <v>466067</v>
       </c>
       <c r="R33" t="n">
-        <v>6809222</v>
+        <v>6809228</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4184,7 +4184,7 @@
         <v>127153911</v>
       </c>
       <c r="B35" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153801</v>
+        <v>127153754</v>
       </c>
       <c r="B36" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,26 +4294,35 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4321,10 +4330,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466383</v>
+        <v>466399</v>
       </c>
       <c r="R36" t="n">
-        <v>6809213</v>
+        <v>6809202</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,7 +4374,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4384,10 +4392,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153754</v>
+        <v>127153801</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4395,35 +4403,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4431,10 +4430,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466399</v>
+        <v>466383</v>
       </c>
       <c r="R37" t="n">
-        <v>6809202</v>
+        <v>6809213</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4475,6 +4474,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127153599</v>
+        <v>127153858</v>
       </c>
       <c r="B38" t="n">
-        <v>79043</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,41 +4504,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466439</v>
+        <v>466333</v>
       </c>
       <c r="R38" t="n">
-        <v>6809218</v>
+        <v>6809211</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4598,10 +4594,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127153858</v>
+        <v>127155517</v>
       </c>
       <c r="B39" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4636,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466333</v>
+        <v>466108</v>
       </c>
       <c r="R39" t="n">
-        <v>6809211</v>
+        <v>6809230</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,10 +4695,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127155517</v>
+        <v>127153599</v>
       </c>
       <c r="B40" t="n">
-        <v>79011</v>
+        <v>79046</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4710,37 +4706,41 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466108</v>
+        <v>466439</v>
       </c>
       <c r="R40" t="n">
-        <v>6809230</v>
+        <v>6809218</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4803,7 +4803,7 @@
         <v>127153795</v>
       </c>
       <c r="B41" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>127154614</v>
       </c>
       <c r="B42" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5015,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127153812</v>
+        <v>127153697</v>
       </c>
       <c r="B43" t="n">
-        <v>79011</v>
+        <v>91343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5026,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466380</v>
+        <v>466269</v>
       </c>
       <c r="R43" t="n">
-        <v>6809217</v>
+        <v>6809223</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,6 +5091,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5104,12 +5109,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5119,7 +5124,7 @@
         <v>127155443</v>
       </c>
       <c r="B44" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5217,10 +5222,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127153697</v>
+        <v>127153812</v>
       </c>
       <c r="B45" t="n">
-        <v>91337</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5228,21 +5233,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5255,10 +5260,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466269</v>
+        <v>466380</v>
       </c>
       <c r="R45" t="n">
-        <v>6809223</v>
+        <v>6809217</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5293,11 +5298,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5311,12 +5311,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -1633,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153712</v>
+        <v>127153532</v>
       </c>
       <c r="B11" t="n">
         <v>79014</v>
@@ -1667,14 +1667,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466164</v>
+        <v>466439</v>
       </c>
       <c r="R11" t="n">
-        <v>6809202</v>
+        <v>6809218</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,11 +1709,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1727,19 +1722,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153532</v>
+        <v>127153712</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1773,14 +1768,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466439</v>
+        <v>466164</v>
       </c>
       <c r="R12" t="n">
-        <v>6809218</v>
+        <v>6809202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,6 +1810,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1828,12 +1828,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2060,7 +2060,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155475</v>
+        <v>127155565</v>
       </c>
       <c r="B15" t="n">
         <v>79014</v>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466076</v>
+        <v>466242</v>
       </c>
       <c r="R15" t="n">
-        <v>6809225</v>
+        <v>6809226</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2161,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127155565</v>
+        <v>127153742</v>
       </c>
       <c r="B16" t="n">
         <v>79014</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466242</v>
+        <v>466410</v>
       </c>
       <c r="R16" t="n">
-        <v>6809226</v>
+        <v>6809205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127153742</v>
+        <v>127155475</v>
       </c>
       <c r="B17" t="n">
         <v>79014</v>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466410</v>
+        <v>466076</v>
       </c>
       <c r="R17" t="n">
-        <v>6809205</v>
+        <v>6809225</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3119,7 +3119,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127154119</v>
+        <v>127154177</v>
       </c>
       <c r="B25" t="n">
         <v>79014</v>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466247</v>
+        <v>466206</v>
       </c>
       <c r="R25" t="n">
-        <v>6809203</v>
+        <v>6809201</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127154177</v>
+        <v>127153768</v>
       </c>
       <c r="B26" t="n">
         <v>79014</v>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466206</v>
+        <v>466392</v>
       </c>
       <c r="R26" t="n">
-        <v>6809201</v>
+        <v>6809204</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,6 +3294,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3321,7 +3326,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127153768</v>
+        <v>127154119</v>
       </c>
       <c r="B27" t="n">
         <v>79014</v>
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466392</v>
+        <v>466247</v>
       </c>
       <c r="R27" t="n">
-        <v>6809204</v>
+        <v>6809203</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,11 +3400,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4074,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127153408</v>
+        <v>127153911</v>
       </c>
       <c r="B34" t="n">
-        <v>5176</v>
+        <v>97320</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,43 +4085,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466439</v>
+        <v>466299</v>
       </c>
       <c r="R34" t="n">
-        <v>6809218</v>
+        <v>6809206</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4181,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127153911</v>
+        <v>127153408</v>
       </c>
       <c r="B35" t="n">
-        <v>97320</v>
+        <v>5176</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4192,38 +4187,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466299</v>
+        <v>466439</v>
       </c>
       <c r="R35" t="n">
-        <v>6809206</v>
+        <v>6809218</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153754</v>
+        <v>127153801</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,35 +4294,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4330,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466399</v>
+        <v>466383</v>
       </c>
       <c r="R36" t="n">
-        <v>6809202</v>
+        <v>6809213</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,6 +4365,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4392,10 +4384,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153801</v>
+        <v>127153754</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4403,26 +4395,35 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4430,10 +4431,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466383</v>
+        <v>466399</v>
       </c>
       <c r="R37" t="n">
-        <v>6809213</v>
+        <v>6809202</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,7 +4475,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5015,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127153697</v>
+        <v>127153812</v>
       </c>
       <c r="B43" t="n">
-        <v>91343</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5026,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466269</v>
+        <v>466380</v>
       </c>
       <c r="R43" t="n">
-        <v>6809223</v>
+        <v>6809217</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,11 +5091,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5109,12 +5104,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5222,10 +5217,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127153812</v>
+        <v>127153697</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>91343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5233,21 +5228,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5260,10 +5255,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466380</v>
+        <v>466269</v>
       </c>
       <c r="R45" t="n">
-        <v>6809217</v>
+        <v>6809223</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5298,6 +5293,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5311,12 +5311,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -2582,46 +2582,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127153709</v>
+        <v>127154181</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>98359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2629,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466410</v>
+        <v>466206</v>
       </c>
       <c r="R20" t="n">
-        <v>6809209</v>
+        <v>6809201</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,17 +2659,13 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2696,38 +2684,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127154181</v>
+        <v>127153709</v>
       </c>
       <c r="B21" t="n">
-        <v>98359</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2735,10 +2731,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466206</v>
+        <v>466410</v>
       </c>
       <c r="R21" t="n">
-        <v>6809201</v>
+        <v>6809209</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,13 +2769,17 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127153768</v>
+        <v>127153920</v>
       </c>
       <c r="B26" t="n">
         <v>79014</v>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466392</v>
+        <v>466298</v>
       </c>
       <c r="R26" t="n">
-        <v>6809204</v>
+        <v>6809205</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,11 +3294,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3326,7 +3321,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127154119</v>
+        <v>127153768</v>
       </c>
       <c r="B27" t="n">
         <v>79014</v>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466247</v>
+        <v>466392</v>
       </c>
       <c r="R27" t="n">
-        <v>6809203</v>
+        <v>6809204</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3400,6 +3395,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127153920</v>
+        <v>127154119</v>
       </c>
       <c r="B28" t="n">
         <v>79014</v>
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466298</v>
+        <v>466247</v>
       </c>
       <c r="R28" t="n">
-        <v>6809205</v>
+        <v>6809203</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3528,46 +3528,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127154103</v>
+        <v>127153894</v>
       </c>
       <c r="B29" t="n">
-        <v>57657</v>
+        <v>98463</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466254</v>
+        <v>466299</v>
       </c>
       <c r="R29" t="n">
-        <v>6809208</v>
+        <v>6809206</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3619,6 +3619,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3637,46 +3638,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127153894</v>
+        <v>127154103</v>
       </c>
       <c r="B30" t="n">
-        <v>98463</v>
+        <v>57657</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3684,10 +3685,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466299</v>
+        <v>466254</v>
       </c>
       <c r="R30" t="n">
-        <v>6809206</v>
+        <v>6809208</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3728,7 +3729,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153801</v>
+        <v>127153754</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,26 +4294,35 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4321,10 +4330,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466383</v>
+        <v>466399</v>
       </c>
       <c r="R36" t="n">
-        <v>6809213</v>
+        <v>6809202</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,7 +4374,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4384,10 +4392,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153754</v>
+        <v>127153801</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4395,35 +4403,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4431,10 +4430,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466399</v>
+        <v>466383</v>
       </c>
       <c r="R37" t="n">
-        <v>6809202</v>
+        <v>6809213</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4475,6 +4474,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5015,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127153812</v>
+        <v>127153697</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>91343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5026,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466380</v>
+        <v>466269</v>
       </c>
       <c r="R43" t="n">
-        <v>6809217</v>
+        <v>6809223</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,6 +5091,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5104,19 +5109,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127155443</v>
+        <v>127153812</v>
       </c>
       <c r="B44" t="n">
         <v>79014</v>
@@ -5154,10 +5159,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466062</v>
+        <v>466380</v>
       </c>
       <c r="R44" t="n">
-        <v>6809234</v>
+        <v>6809217</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5217,10 +5222,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127153697</v>
+        <v>127155443</v>
       </c>
       <c r="B45" t="n">
-        <v>91343</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5228,21 +5233,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5255,10 +5260,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466269</v>
+        <v>466062</v>
       </c>
       <c r="R45" t="n">
-        <v>6809223</v>
+        <v>6809234</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5293,11 +5298,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5311,12 +5311,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>127154126</v>
       </c>
       <c r="B3" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127154078</v>
+        <v>127154595</v>
       </c>
       <c r="B9" t="n">
         <v>57657</v>
@@ -1445,14 +1445,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466256</v>
+        <v>466128</v>
       </c>
       <c r="R9" t="n">
-        <v>6809224</v>
+        <v>6809202</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127154595</v>
+        <v>127154078</v>
       </c>
       <c r="B10" t="n">
         <v>57657</v>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466128</v>
+        <v>466256</v>
       </c>
       <c r="R10" t="n">
-        <v>6809202</v>
+        <v>6809224</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153532</v>
+        <v>127153712</v>
       </c>
       <c r="B11" t="n">
         <v>79014</v>
@@ -1667,14 +1667,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466439</v>
+        <v>466164</v>
       </c>
       <c r="R11" t="n">
-        <v>6809218</v>
+        <v>6809202</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1709,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1722,19 +1727,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153712</v>
+        <v>127153532</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1768,14 +1773,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466164</v>
+        <v>466439</v>
       </c>
       <c r="R12" t="n">
-        <v>6809202</v>
+        <v>6809218</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,11 +1815,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1828,12 +1828,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1843,7 +1843,7 @@
         <v>127153879</v>
       </c>
       <c r="B13" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>127154092</v>
       </c>
       <c r="B14" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155565</v>
+        <v>127155475</v>
       </c>
       <c r="B15" t="n">
         <v>79014</v>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466242</v>
+        <v>466076</v>
       </c>
       <c r="R15" t="n">
-        <v>6809226</v>
+        <v>6809225</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2161,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127153742</v>
+        <v>127155565</v>
       </c>
       <c r="B16" t="n">
         <v>79014</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466410</v>
+        <v>466242</v>
       </c>
       <c r="R16" t="n">
-        <v>6809205</v>
+        <v>6809226</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127155475</v>
+        <v>127153742</v>
       </c>
       <c r="B17" t="n">
         <v>79014</v>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466076</v>
+        <v>466410</v>
       </c>
       <c r="R17" t="n">
-        <v>6809225</v>
+        <v>6809205</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2363,46 +2363,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127154600</v>
+        <v>127154066</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>98464</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466144</v>
+        <v>466274</v>
       </c>
       <c r="R18" t="n">
-        <v>6809220</v>
+        <v>6809202</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,6 +2454,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2472,46 +2473,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127154066</v>
+        <v>127154600</v>
       </c>
       <c r="B19" t="n">
-        <v>98463</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2519,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466274</v>
+        <v>466144</v>
       </c>
       <c r="R19" t="n">
-        <v>6809202</v>
+        <v>6809220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,7 +2564,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>127154181</v>
       </c>
       <c r="B20" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127154177</v>
+        <v>127154119</v>
       </c>
       <c r="B25" t="n">
         <v>79014</v>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466206</v>
+        <v>466247</v>
       </c>
       <c r="R25" t="n">
-        <v>6809201</v>
+        <v>6809203</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127153920</v>
+        <v>127154177</v>
       </c>
       <c r="B26" t="n">
         <v>79014</v>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466298</v>
+        <v>466206</v>
       </c>
       <c r="R26" t="n">
-        <v>6809205</v>
+        <v>6809201</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3427,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127154119</v>
+        <v>127153920</v>
       </c>
       <c r="B28" t="n">
         <v>79014</v>
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466247</v>
+        <v>466298</v>
       </c>
       <c r="R28" t="n">
-        <v>6809203</v>
+        <v>6809205</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3528,46 +3528,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127153894</v>
+        <v>127154103</v>
       </c>
       <c r="B29" t="n">
-        <v>98463</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466299</v>
+        <v>466254</v>
       </c>
       <c r="R29" t="n">
-        <v>6809206</v>
+        <v>6809208</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3619,7 +3619,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3638,46 +3637,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127154103</v>
+        <v>127153894</v>
       </c>
       <c r="B30" t="n">
-        <v>57657</v>
+        <v>98464</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3685,10 +3684,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466254</v>
+        <v>466299</v>
       </c>
       <c r="R30" t="n">
-        <v>6809208</v>
+        <v>6809206</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3729,6 +3728,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127154630</v>
+        <v>127154111</v>
       </c>
       <c r="B31" t="n">
-        <v>56849</v>
+        <v>57657</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3784,7 +3784,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466148</v>
+        <v>466259</v>
       </c>
       <c r="R31" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127154111</v>
+        <v>127155460</v>
       </c>
       <c r="B32" t="n">
         <v>57657</v>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466259</v>
+        <v>466067</v>
       </c>
       <c r="R32" t="n">
-        <v>6809208</v>
+        <v>6809228</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127155460</v>
+        <v>127154630</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>56849</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466067</v>
+        <v>466148</v>
       </c>
       <c r="R33" t="n">
-        <v>6809228</v>
+        <v>6809222</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4074,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127153911</v>
+        <v>127153408</v>
       </c>
       <c r="B34" t="n">
-        <v>97320</v>
+        <v>5176</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,38 +4085,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466299</v>
+        <v>466439</v>
       </c>
       <c r="R34" t="n">
-        <v>6809206</v>
+        <v>6809218</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4176,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127153408</v>
+        <v>127153911</v>
       </c>
       <c r="B35" t="n">
-        <v>5176</v>
+        <v>97321</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,43 +4192,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466439</v>
+        <v>466299</v>
       </c>
       <c r="R35" t="n">
-        <v>6809218</v>
+        <v>6809206</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153754</v>
+        <v>127153801</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,35 +4294,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4330,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466399</v>
+        <v>466383</v>
       </c>
       <c r="R36" t="n">
-        <v>6809202</v>
+        <v>6809213</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,6 +4365,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4392,10 +4384,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153801</v>
+        <v>127153754</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4403,26 +4395,35 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4430,10 +4431,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466383</v>
+        <v>466399</v>
       </c>
       <c r="R37" t="n">
-        <v>6809213</v>
+        <v>6809202</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,7 +4475,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4800,36 +4800,44 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127153795</v>
+        <v>127154614</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>80083</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4838,10 +4846,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466388</v>
+        <v>466148</v>
       </c>
       <c r="R41" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4874,6 +4882,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4901,44 +4914,36 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127154614</v>
+        <v>127153795</v>
       </c>
       <c r="B42" t="n">
-        <v>80083</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4947,10 +4952,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466148</v>
+        <v>466388</v>
       </c>
       <c r="R42" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4983,11 +4988,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5015,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127153697</v>
+        <v>127155443</v>
       </c>
       <c r="B43" t="n">
-        <v>91343</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5026,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466269</v>
+        <v>466062</v>
       </c>
       <c r="R43" t="n">
-        <v>6809223</v>
+        <v>6809234</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,11 +5091,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5109,12 +5104,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5222,10 +5217,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127155443</v>
+        <v>127153697</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>91344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5233,21 +5228,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5260,10 +5255,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466062</v>
+        <v>466269</v>
       </c>
       <c r="R45" t="n">
-        <v>6809234</v>
+        <v>6809223</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5298,6 +5293,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5311,12 +5311,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -1633,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153712</v>
+        <v>127153532</v>
       </c>
       <c r="B11" t="n">
         <v>79014</v>
@@ -1667,14 +1667,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466164</v>
+        <v>466439</v>
       </c>
       <c r="R11" t="n">
-        <v>6809202</v>
+        <v>6809218</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,11 +1709,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1727,19 +1722,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153532</v>
+        <v>127153712</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1773,14 +1768,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466439</v>
+        <v>466164</v>
       </c>
       <c r="R12" t="n">
-        <v>6809218</v>
+        <v>6809202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,6 +1810,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1828,12 +1828,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2582,38 +2582,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127154181</v>
+        <v>127153709</v>
       </c>
       <c r="B20" t="n">
-        <v>98360</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2621,10 +2629,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466206</v>
+        <v>466410</v>
       </c>
       <c r="R20" t="n">
-        <v>6809201</v>
+        <v>6809209</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,13 +2667,17 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2684,46 +2696,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127153709</v>
+        <v>127154181</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>98360</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2731,10 +2735,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466410</v>
+        <v>466206</v>
       </c>
       <c r="R21" t="n">
-        <v>6809209</v>
+        <v>6809201</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,17 +2773,13 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -1734,37 +1734,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153712</v>
+        <v>127153879</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1772,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466164</v>
+        <v>466321</v>
       </c>
       <c r="R12" t="n">
-        <v>6809202</v>
+        <v>6809223</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,11 +1819,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1828,58 +1832,49 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153879</v>
+        <v>127153712</v>
       </c>
       <c r="B13" t="n">
-        <v>98464</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466321</v>
+        <v>466164</v>
       </c>
       <c r="R13" t="n">
-        <v>6809223</v>
+        <v>6809202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,6 +1920,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1938,12 +1938,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2060,7 +2060,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155475</v>
+        <v>127155565</v>
       </c>
       <c r="B15" t="n">
         <v>79014</v>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466076</v>
+        <v>466242</v>
       </c>
       <c r="R15" t="n">
-        <v>6809225</v>
+        <v>6809226</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2161,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127155565</v>
+        <v>127153742</v>
       </c>
       <c r="B16" t="n">
         <v>79014</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466242</v>
+        <v>466410</v>
       </c>
       <c r="R16" t="n">
-        <v>6809226</v>
+        <v>6809205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127153742</v>
+        <v>127155475</v>
       </c>
       <c r="B17" t="n">
         <v>79014</v>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466410</v>
+        <v>466076</v>
       </c>
       <c r="R17" t="n">
-        <v>6809205</v>
+        <v>6809225</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2363,46 +2363,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127154066</v>
+        <v>127154600</v>
       </c>
       <c r="B18" t="n">
-        <v>98464</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466274</v>
+        <v>466144</v>
       </c>
       <c r="R18" t="n">
-        <v>6809202</v>
+        <v>6809220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,7 +2454,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2473,46 +2472,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127154600</v>
+        <v>127154066</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>98464</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2520,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466144</v>
+        <v>466274</v>
       </c>
       <c r="R19" t="n">
-        <v>6809220</v>
+        <v>6809202</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,6 +2563,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3119,7 +3119,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127154119</v>
+        <v>127154177</v>
       </c>
       <c r="B25" t="n">
         <v>79014</v>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466247</v>
+        <v>466206</v>
       </c>
       <c r="R25" t="n">
-        <v>6809203</v>
+        <v>6809201</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127154177</v>
+        <v>127153768</v>
       </c>
       <c r="B26" t="n">
         <v>79014</v>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466206</v>
+        <v>466392</v>
       </c>
       <c r="R26" t="n">
-        <v>6809201</v>
+        <v>6809204</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,6 +3294,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3321,7 +3326,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127153768</v>
+        <v>127154119</v>
       </c>
       <c r="B27" t="n">
         <v>79014</v>
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466392</v>
+        <v>466247</v>
       </c>
       <c r="R27" t="n">
-        <v>6809204</v>
+        <v>6809203</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,11 +3400,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3747,7 +3747,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127154111</v>
+        <v>127155460</v>
       </c>
       <c r="B31" t="n">
         <v>57657</v>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466259</v>
+        <v>466067</v>
       </c>
       <c r="R31" t="n">
-        <v>6809208</v>
+        <v>6809228</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,32 +3856,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127155460</v>
+        <v>127154630</v>
       </c>
       <c r="B32" t="n">
-        <v>57657</v>
+        <v>56849</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3893,7 +3893,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466067</v>
+        <v>466148</v>
       </c>
       <c r="R32" t="n">
-        <v>6809228</v>
+        <v>6809222</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127154630</v>
+        <v>127154111</v>
       </c>
       <c r="B33" t="n">
-        <v>56849</v>
+        <v>57657</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466148</v>
+        <v>466259</v>
       </c>
       <c r="R33" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127153858</v>
+        <v>127153599</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,37 +4504,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466333</v>
+        <v>466439</v>
       </c>
       <c r="R38" t="n">
-        <v>6809211</v>
+        <v>6809218</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4594,7 +4598,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127155517</v>
+        <v>127153858</v>
       </c>
       <c r="B39" t="n">
         <v>79014</v>
@@ -4632,10 +4636,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466108</v>
+        <v>466333</v>
       </c>
       <c r="R39" t="n">
-        <v>6809230</v>
+        <v>6809211</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4695,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127153599</v>
+        <v>127155517</v>
       </c>
       <c r="B40" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4706,41 +4710,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466439</v>
+        <v>466108</v>
       </c>
       <c r="R40" t="n">
-        <v>6809218</v>
+        <v>6809230</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4800,44 +4800,36 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127154614</v>
+        <v>127153795</v>
       </c>
       <c r="B41" t="n">
-        <v>80083</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4846,10 +4838,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466148</v>
+        <v>466388</v>
       </c>
       <c r="R41" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4882,11 +4874,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4914,36 +4901,44 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127153795</v>
+        <v>127154614</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>80083</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4952,10 +4947,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466388</v>
+        <v>466148</v>
       </c>
       <c r="R42" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4988,6 +4983,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5015,7 +5015,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127155443</v>
+        <v>127153812</v>
       </c>
       <c r="B43" t="n">
         <v>79014</v>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466062</v>
+        <v>466380</v>
       </c>
       <c r="R43" t="n">
-        <v>6809234</v>
+        <v>6809217</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5116,7 +5116,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127153812</v>
+        <v>127155443</v>
       </c>
       <c r="B44" t="n">
         <v>79014</v>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466380</v>
+        <v>466062</v>
       </c>
       <c r="R44" t="n">
-        <v>6809217</v>
+        <v>6809234</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -1734,46 +1734,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153879</v>
+        <v>127153712</v>
       </c>
       <c r="B12" t="n">
-        <v>98464</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1781,10 +1772,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466321</v>
+        <v>466164</v>
       </c>
       <c r="R12" t="n">
-        <v>6809223</v>
+        <v>6809202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,6 +1810,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1832,49 +1828,58 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153712</v>
+        <v>127153879</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466164</v>
+        <v>466321</v>
       </c>
       <c r="R13" t="n">
-        <v>6809202</v>
+        <v>6809223</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,11 +1925,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1938,12 +1938,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -4074,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127153408</v>
+        <v>127153911</v>
       </c>
       <c r="B34" t="n">
-        <v>5176</v>
+        <v>97321</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,43 +4085,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466439</v>
+        <v>466299</v>
       </c>
       <c r="R34" t="n">
-        <v>6809218</v>
+        <v>6809206</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4181,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127153911</v>
+        <v>127153408</v>
       </c>
       <c r="B35" t="n">
-        <v>97321</v>
+        <v>5176</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4192,38 +4187,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466299</v>
+        <v>466439</v>
       </c>
       <c r="R35" t="n">
-        <v>6809206</v>
+        <v>6809218</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127153844</v>
       </c>
       <c r="B2" t="n">
-        <v>80145</v>
+        <v>80149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127154126</v>
       </c>
       <c r="B3" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>127153831</v>
       </c>
       <c r="B4" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127155482</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>127153848</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>127153643</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>127155380</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127154595</v>
+        <v>127154078</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,14 +1445,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466128</v>
+        <v>466256</v>
       </c>
       <c r="R9" t="n">
-        <v>6809202</v>
+        <v>6809224</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127154078</v>
+        <v>127154595</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466256</v>
+        <v>466128</v>
       </c>
       <c r="R10" t="n">
-        <v>6809224</v>
+        <v>6809202</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,48 +1633,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153532</v>
+        <v>127153879</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>98468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466439</v>
+        <v>466321</v>
       </c>
       <c r="R11" t="n">
-        <v>6809218</v>
+        <v>6809223</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153712</v>
+        <v>127153532</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1768,14 +1777,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466164</v>
+        <v>466439</v>
       </c>
       <c r="R12" t="n">
-        <v>6809202</v>
+        <v>6809218</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,11 +1819,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1828,58 +1832,49 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153879</v>
+        <v>127153712</v>
       </c>
       <c r="B13" t="n">
-        <v>98464</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466321</v>
+        <v>466164</v>
       </c>
       <c r="R13" t="n">
-        <v>6809223</v>
+        <v>6809202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,6 +1920,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1938,12 +1938,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1953,7 +1953,7 @@
         <v>127154092</v>
       </c>
       <c r="B14" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155565</v>
+        <v>127153742</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466242</v>
+        <v>466410</v>
       </c>
       <c r="R15" t="n">
-        <v>6809226</v>
+        <v>6809205</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127153742</v>
+        <v>127155565</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466410</v>
+        <v>466242</v>
       </c>
       <c r="R16" t="n">
-        <v>6809205</v>
+        <v>6809226</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
         <v>127155475</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>127154600</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>127154066</v>
       </c>
       <c r="B19" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>127153709</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>127154181</v>
       </c>
       <c r="B21" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>127155499</v>
       </c>
       <c r="B22" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>127153899</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>127155506</v>
       </c>
       <c r="B24" t="n">
-        <v>5196</v>
+        <v>5197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127154177</v>
+        <v>127153768</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466206</v>
+        <v>466392</v>
       </c>
       <c r="R25" t="n">
-        <v>6809201</v>
+        <v>6809204</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3193,6 +3193,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3220,10 +3225,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127153768</v>
+        <v>127153920</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3258,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466392</v>
+        <v>466298</v>
       </c>
       <c r="R26" t="n">
-        <v>6809204</v>
+        <v>6809205</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,11 +3299,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3326,10 +3326,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127154119</v>
+        <v>127154177</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466247</v>
+        <v>466206</v>
       </c>
       <c r="R27" t="n">
-        <v>6809203</v>
+        <v>6809201</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3427,10 +3427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127153920</v>
+        <v>127154119</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466298</v>
+        <v>466247</v>
       </c>
       <c r="R28" t="n">
-        <v>6809205</v>
+        <v>6809203</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,7 +3531,7 @@
         <v>127154103</v>
       </c>
       <c r="B29" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>127153894</v>
       </c>
       <c r="B30" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127155460</v>
+        <v>127154111</v>
       </c>
       <c r="B31" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466067</v>
+        <v>466259</v>
       </c>
       <c r="R31" t="n">
-        <v>6809228</v>
+        <v>6809208</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,32 +3856,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127154630</v>
+        <v>127155460</v>
       </c>
       <c r="B32" t="n">
-        <v>56849</v>
+        <v>57661</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3893,7 +3893,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466148</v>
+        <v>466067</v>
       </c>
       <c r="R32" t="n">
-        <v>6809222</v>
+        <v>6809228</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127154111</v>
+        <v>127154630</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>56853</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466259</v>
+        <v>466148</v>
       </c>
       <c r="R33" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4074,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127153911</v>
+        <v>127153408</v>
       </c>
       <c r="B34" t="n">
-        <v>97321</v>
+        <v>5177</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,38 +4085,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466299</v>
+        <v>466439</v>
       </c>
       <c r="R34" t="n">
-        <v>6809206</v>
+        <v>6809218</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4176,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127153408</v>
+        <v>127153911</v>
       </c>
       <c r="B35" t="n">
-        <v>5176</v>
+        <v>97325</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,43 +4192,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466439</v>
+        <v>466299</v>
       </c>
       <c r="R35" t="n">
-        <v>6809218</v>
+        <v>6809206</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4286,7 +4286,7 @@
         <v>127153801</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>127153754</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127153599</v>
+        <v>127153858</v>
       </c>
       <c r="B38" t="n">
-        <v>79046</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,41 +4504,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466439</v>
+        <v>466333</v>
       </c>
       <c r="R38" t="n">
-        <v>6809218</v>
+        <v>6809211</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4598,10 +4594,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127153858</v>
+        <v>127153599</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>79050</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4609,37 +4605,41 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466333</v>
+        <v>466439</v>
       </c>
       <c r="R39" t="n">
-        <v>6809211</v>
+        <v>6809218</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4702,7 +4702,7 @@
         <v>127155517</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>127153795</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>127154614</v>
       </c>
       <c r="B42" t="n">
-        <v>80083</v>
+        <v>80087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>127153812</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5116,10 +5116,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127155443</v>
+        <v>127153697</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>91348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5127,21 +5127,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466062</v>
+        <v>466269</v>
       </c>
       <c r="R44" t="n">
-        <v>6809234</v>
+        <v>6809223</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5192,6 +5192,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5205,22 +5210,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127153697</v>
+        <v>127155443</v>
       </c>
       <c r="B45" t="n">
-        <v>91344</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5228,21 +5233,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5255,10 +5260,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466269</v>
+        <v>466062</v>
       </c>
       <c r="R45" t="n">
-        <v>6809223</v>
+        <v>6809234</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5293,11 +5298,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5311,12 +5311,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127153844</v>
+        <v>127154126</v>
       </c>
       <c r="B2" t="n">
-        <v>80149</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466359</v>
+        <v>466247</v>
       </c>
       <c r="R2" t="n">
-        <v>6809211</v>
+        <v>6809203</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127154126</v>
+        <v>127153844</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,35 +796,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466247</v>
+        <v>466359</v>
       </c>
       <c r="R3" t="n">
-        <v>6809203</v>
+        <v>6809211</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1633,57 +1633,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153879</v>
+        <v>127153532</v>
       </c>
       <c r="B11" t="n">
-        <v>98468</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466321</v>
+        <v>466439</v>
       </c>
       <c r="R11" t="n">
-        <v>6809223</v>
+        <v>6809218</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1734,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153532</v>
+        <v>127153712</v>
       </c>
       <c r="B12" t="n">
         <v>79018</v>
@@ -1777,14 +1768,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466439</v>
+        <v>466164</v>
       </c>
       <c r="R12" t="n">
-        <v>6809218</v>
+        <v>6809202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,6 +1810,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1832,49 +1828,58 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153712</v>
+        <v>127153879</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466164</v>
+        <v>466321</v>
       </c>
       <c r="R13" t="n">
-        <v>6809202</v>
+        <v>6809223</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,11 +1925,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1938,12 +1938,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2060,7 +2060,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127153742</v>
+        <v>127155565</v>
       </c>
       <c r="B15" t="n">
         <v>79018</v>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466410</v>
+        <v>466242</v>
       </c>
       <c r="R15" t="n">
-        <v>6809205</v>
+        <v>6809226</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2161,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127155565</v>
+        <v>127153742</v>
       </c>
       <c r="B16" t="n">
         <v>79018</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466242</v>
+        <v>466410</v>
       </c>
       <c r="R16" t="n">
-        <v>6809226</v>
+        <v>6809205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2907,27 +2907,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127153899</v>
+        <v>127155506</v>
       </c>
       <c r="B23" t="n">
-        <v>57661</v>
+        <v>5197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2936,11 +2936,12 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2950,10 +2951,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466299</v>
+        <v>466085</v>
       </c>
       <c r="R23" t="n">
-        <v>6809206</v>
+        <v>6809224</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2994,6 +2995,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3012,27 +3014,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127155506</v>
+        <v>127153899</v>
       </c>
       <c r="B24" t="n">
-        <v>5197</v>
+        <v>57661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3041,12 +3043,11 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3056,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466085</v>
+        <v>466299</v>
       </c>
       <c r="R24" t="n">
-        <v>6809224</v>
+        <v>6809206</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3100,7 +3101,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3119,7 +3119,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127153768</v>
+        <v>127154177</v>
       </c>
       <c r="B25" t="n">
         <v>79018</v>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466392</v>
+        <v>466206</v>
       </c>
       <c r="R25" t="n">
-        <v>6809204</v>
+        <v>6809201</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3193,11 +3193,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3225,7 +3220,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127153920</v>
+        <v>127153768</v>
       </c>
       <c r="B26" t="n">
         <v>79018</v>
@@ -3263,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466298</v>
+        <v>466392</v>
       </c>
       <c r="R26" t="n">
-        <v>6809205</v>
+        <v>6809204</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3299,6 +3294,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3326,7 +3326,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127154177</v>
+        <v>127154119</v>
       </c>
       <c r="B27" t="n">
         <v>79018</v>
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466206</v>
+        <v>466247</v>
       </c>
       <c r="R27" t="n">
-        <v>6809201</v>
+        <v>6809203</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3427,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127154119</v>
+        <v>127153920</v>
       </c>
       <c r="B28" t="n">
         <v>79018</v>
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466247</v>
+        <v>466298</v>
       </c>
       <c r="R28" t="n">
-        <v>6809203</v>
+        <v>6809205</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4594,10 +4594,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127153599</v>
+        <v>127155517</v>
       </c>
       <c r="B39" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4605,41 +4605,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466439</v>
+        <v>466108</v>
       </c>
       <c r="R39" t="n">
-        <v>6809218</v>
+        <v>6809230</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,10 +4695,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127155517</v>
+        <v>127153599</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4710,37 +4706,41 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466108</v>
+        <v>466439</v>
       </c>
       <c r="R40" t="n">
-        <v>6809230</v>
+        <v>6809218</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5116,10 +5116,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127153697</v>
+        <v>127155443</v>
       </c>
       <c r="B44" t="n">
-        <v>91348</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5127,21 +5127,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466269</v>
+        <v>466062</v>
       </c>
       <c r="R44" t="n">
-        <v>6809223</v>
+        <v>6809234</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5192,11 +5192,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5210,22 +5205,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127155443</v>
+        <v>127153697</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>91348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5233,21 +5228,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5260,10 +5255,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466062</v>
+        <v>466269</v>
       </c>
       <c r="R45" t="n">
-        <v>6809234</v>
+        <v>6809223</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5298,6 +5293,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5311,12 +5311,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127154126</v>
+        <v>127153844</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>80149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,35 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466247</v>
+        <v>466359</v>
       </c>
       <c r="R2" t="n">
-        <v>6809203</v>
+        <v>6809211</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127153844</v>
+        <v>127154126</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,26 +787,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466359</v>
+        <v>466247</v>
       </c>
       <c r="R3" t="n">
-        <v>6809211</v>
+        <v>6809203</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -2798,10 +2798,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127155499</v>
+        <v>127153899</v>
       </c>
       <c r="B22" t="n">
-        <v>57658</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2809,16 +2809,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2826,11 +2826,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
@@ -2845,10 +2841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466085</v>
+        <v>466299</v>
       </c>
       <c r="R22" t="n">
-        <v>6809224</v>
+        <v>6809206</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,27 +2903,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127155506</v>
+        <v>127155499</v>
       </c>
       <c r="B23" t="n">
-        <v>5197</v>
+        <v>57658</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2935,13 +2931,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2995,7 +2994,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3014,27 +3012,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127153899</v>
+        <v>127155506</v>
       </c>
       <c r="B24" t="n">
-        <v>57661</v>
+        <v>5197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3043,11 +3041,12 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3057,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466299</v>
+        <v>466085</v>
       </c>
       <c r="R24" t="n">
-        <v>6809206</v>
+        <v>6809224</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3101,6 +3100,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127154111</v>
+        <v>127154630</v>
       </c>
       <c r="B31" t="n">
-        <v>57661</v>
+        <v>56853</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3784,7 +3784,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466259</v>
+        <v>466148</v>
       </c>
       <c r="R31" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127155460</v>
+        <v>127154111</v>
       </c>
       <c r="B32" t="n">
         <v>57661</v>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466067</v>
+        <v>466259</v>
       </c>
       <c r="R32" t="n">
-        <v>6809228</v>
+        <v>6809208</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127154630</v>
+        <v>127155460</v>
       </c>
       <c r="B33" t="n">
-        <v>56853</v>
+        <v>57661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466148</v>
+        <v>466067</v>
       </c>
       <c r="R33" t="n">
-        <v>6809222</v>
+        <v>6809228</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -3747,32 +3747,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127154630</v>
+        <v>127154111</v>
       </c>
       <c r="B31" t="n">
-        <v>56853</v>
+        <v>57661</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3784,7 +3784,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466148</v>
+        <v>466259</v>
       </c>
       <c r="R31" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127154111</v>
+        <v>127155460</v>
       </c>
       <c r="B32" t="n">
         <v>57661</v>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466259</v>
+        <v>466067</v>
       </c>
       <c r="R32" t="n">
-        <v>6809208</v>
+        <v>6809228</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127155460</v>
+        <v>127154630</v>
       </c>
       <c r="B33" t="n">
-        <v>57661</v>
+        <v>56853</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466067</v>
+        <v>466148</v>
       </c>
       <c r="R33" t="n">
-        <v>6809228</v>
+        <v>6809222</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>127154126</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127155380</v>
+        <v>127154078</v>
       </c>
       <c r="B8" t="n">
         <v>57661</v>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466021</v>
+        <v>466256</v>
       </c>
       <c r="R8" t="n">
-        <v>6809226</v>
+        <v>6809224</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127154078</v>
+        <v>127154595</v>
       </c>
       <c r="B9" t="n">
         <v>57661</v>
@@ -1445,14 +1445,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466256</v>
+        <v>466128</v>
       </c>
       <c r="R9" t="n">
-        <v>6809224</v>
+        <v>6809202</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127154595</v>
+        <v>127155380</v>
       </c>
       <c r="B10" t="n">
         <v>57661</v>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466128</v>
+        <v>466021</v>
       </c>
       <c r="R10" t="n">
-        <v>6809202</v>
+        <v>6809226</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,48 +1633,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153532</v>
+        <v>127153879</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>98469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466439</v>
+        <v>466321</v>
       </c>
       <c r="R11" t="n">
-        <v>6809218</v>
+        <v>6809223</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1743,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153712</v>
+        <v>127153532</v>
       </c>
       <c r="B12" t="n">
         <v>79018</v>
@@ -1768,14 +1777,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466164</v>
+        <v>466439</v>
       </c>
       <c r="R12" t="n">
-        <v>6809202</v>
+        <v>6809218</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,11 +1819,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1828,58 +1832,49 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153879</v>
+        <v>127153712</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466321</v>
+        <v>466164</v>
       </c>
       <c r="R13" t="n">
-        <v>6809223</v>
+        <v>6809202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,6 +1920,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1938,12 +1938,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1953,7 +1953,7 @@
         <v>127154092</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>127154066</v>
       </c>
       <c r="B19" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>127154181</v>
       </c>
       <c r="B21" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2798,10 +2798,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127153899</v>
+        <v>127155499</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>57658</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2809,16 +2809,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2826,7 +2826,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
@@ -2841,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466299</v>
+        <v>466085</v>
       </c>
       <c r="R22" t="n">
-        <v>6809206</v>
+        <v>6809224</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2903,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127155499</v>
+        <v>127153899</v>
       </c>
       <c r="B23" t="n">
-        <v>57658</v>
+        <v>57661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2914,16 +2918,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2931,11 +2935,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466085</v>
+        <v>466299</v>
       </c>
       <c r="R23" t="n">
-        <v>6809224</v>
+        <v>6809206</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3640,7 +3640,7 @@
         <v>127153894</v>
       </c>
       <c r="B30" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153801</v>
+        <v>127153754</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,26 +4294,35 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4321,10 +4330,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466383</v>
+        <v>466399</v>
       </c>
       <c r="R36" t="n">
-        <v>6809213</v>
+        <v>6809202</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,7 +4374,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4384,10 +4392,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153754</v>
+        <v>127153801</v>
       </c>
       <c r="B37" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4395,35 +4403,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4431,10 +4430,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466399</v>
+        <v>466383</v>
       </c>
       <c r="R37" t="n">
-        <v>6809202</v>
+        <v>6809213</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4475,6 +4474,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127153858</v>
+        <v>127153599</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,37 +4504,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466333</v>
+        <v>466439</v>
       </c>
       <c r="R38" t="n">
-        <v>6809211</v>
+        <v>6809218</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4594,7 +4598,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127155517</v>
+        <v>127153858</v>
       </c>
       <c r="B39" t="n">
         <v>79018</v>
@@ -4632,10 +4636,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466108</v>
+        <v>466333</v>
       </c>
       <c r="R39" t="n">
-        <v>6809230</v>
+        <v>6809211</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4695,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127153599</v>
+        <v>127155517</v>
       </c>
       <c r="B40" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4706,41 +4710,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466439</v>
+        <v>466108</v>
       </c>
       <c r="R40" t="n">
-        <v>6809218</v>
+        <v>6809230</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127153848</v>
+        <v>127153643</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,37 +1111,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466359</v>
+        <v>466439</v>
       </c>
       <c r="R6" t="n">
-        <v>6809211</v>
+        <v>6809218</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1187,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1201,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127153643</v>
+        <v>127153848</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,42 +1216,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466439</v>
+        <v>466359</v>
       </c>
       <c r="R7" t="n">
-        <v>6809218</v>
+        <v>6809211</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,6 +1287,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -2363,46 +2363,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127154600</v>
+        <v>127154066</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>98469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466144</v>
+        <v>466274</v>
       </c>
       <c r="R18" t="n">
-        <v>6809220</v>
+        <v>6809202</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,6 +2454,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2472,46 +2473,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127154066</v>
+        <v>127154600</v>
       </c>
       <c r="B19" t="n">
-        <v>98469</v>
+        <v>57661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2519,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466274</v>
+        <v>466144</v>
       </c>
       <c r="R19" t="n">
-        <v>6809202</v>
+        <v>6809220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,7 +2564,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127154111</v>
+        <v>127155460</v>
       </c>
       <c r="B31" t="n">
         <v>57661</v>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466259</v>
+        <v>466067</v>
       </c>
       <c r="R31" t="n">
-        <v>6809208</v>
+        <v>6809228</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127155460</v>
+        <v>127154111</v>
       </c>
       <c r="B32" t="n">
         <v>57661</v>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466067</v>
+        <v>466259</v>
       </c>
       <c r="R32" t="n">
-        <v>6809228</v>
+        <v>6809208</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4800,36 +4800,44 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127153795</v>
+        <v>127154614</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>80087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4838,10 +4846,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466388</v>
+        <v>466148</v>
       </c>
       <c r="R41" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4874,6 +4882,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4901,44 +4914,36 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127154614</v>
+        <v>127153795</v>
       </c>
       <c r="B42" t="n">
-        <v>80087</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4947,10 +4952,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466148</v>
+        <v>466388</v>
       </c>
       <c r="R42" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4983,11 +4988,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127153844</v>
       </c>
       <c r="B2" t="n">
-        <v>80149</v>
+        <v>80151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127154126</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>127153831</v>
       </c>
       <c r="B4" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127155482</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>127153643</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127153848</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154078</v>
+        <v>127155380</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466256</v>
+        <v>466021</v>
       </c>
       <c r="R8" t="n">
-        <v>6809224</v>
+        <v>6809226</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127154595</v>
+        <v>127154078</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,14 +1445,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466128</v>
+        <v>466256</v>
       </c>
       <c r="R9" t="n">
-        <v>6809202</v>
+        <v>6809224</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127155380</v>
+        <v>127154595</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466021</v>
+        <v>466128</v>
       </c>
       <c r="R10" t="n">
-        <v>6809226</v>
+        <v>6809202</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,57 +1633,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153879</v>
+        <v>127153532</v>
       </c>
       <c r="B11" t="n">
-        <v>98469</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466321</v>
+        <v>466439</v>
       </c>
       <c r="R11" t="n">
-        <v>6809223</v>
+        <v>6809218</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1734,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153532</v>
+        <v>127153712</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,14 +1768,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466439</v>
+        <v>466164</v>
       </c>
       <c r="R12" t="n">
-        <v>6809218</v>
+        <v>6809202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,6 +1810,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1832,49 +1828,58 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153712</v>
+        <v>127153879</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>98471</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466164</v>
+        <v>466321</v>
       </c>
       <c r="R13" t="n">
-        <v>6809202</v>
+        <v>6809223</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,11 +1925,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1938,12 +1938,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1953,7 +1953,7 @@
         <v>127154092</v>
       </c>
       <c r="B14" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>127155565</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>127153742</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>127155475</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2363,46 +2363,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127154066</v>
+        <v>127154600</v>
       </c>
       <c r="B18" t="n">
-        <v>98469</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466274</v>
+        <v>466144</v>
       </c>
       <c r="R18" t="n">
-        <v>6809202</v>
+        <v>6809220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,7 +2454,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2473,46 +2472,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127154600</v>
+        <v>127154066</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>98471</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2520,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466144</v>
+        <v>466274</v>
       </c>
       <c r="R19" t="n">
-        <v>6809220</v>
+        <v>6809202</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,6 +2563,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>127153709</v>
       </c>
       <c r="B20" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>127154181</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2798,10 +2798,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127155499</v>
+        <v>127153899</v>
       </c>
       <c r="B22" t="n">
-        <v>57658</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2809,16 +2809,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2826,11 +2826,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
@@ -2845,10 +2841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466085</v>
+        <v>466299</v>
       </c>
       <c r="R22" t="n">
-        <v>6809224</v>
+        <v>6809206</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,10 +2903,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127153899</v>
+        <v>127155499</v>
       </c>
       <c r="B23" t="n">
-        <v>57661</v>
+        <v>57660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2918,16 +2914,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2935,7 +2931,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466299</v>
+        <v>466085</v>
       </c>
       <c r="R23" t="n">
-        <v>6809206</v>
+        <v>6809224</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3122,7 +3122,7 @@
         <v>127154177</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>127153768</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>127154119</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>127153920</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>127154103</v>
       </c>
       <c r="B29" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>127153894</v>
       </c>
       <c r="B30" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127155460</v>
+        <v>127154630</v>
       </c>
       <c r="B31" t="n">
-        <v>57661</v>
+        <v>56855</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3784,7 +3784,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466067</v>
+        <v>466148</v>
       </c>
       <c r="R31" t="n">
-        <v>6809228</v>
+        <v>6809222</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3859,7 +3859,7 @@
         <v>127154111</v>
       </c>
       <c r="B32" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127154630</v>
+        <v>127155460</v>
       </c>
       <c r="B33" t="n">
-        <v>56853</v>
+        <v>57663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466148</v>
+        <v>466067</v>
       </c>
       <c r="R33" t="n">
-        <v>6809222</v>
+        <v>6809228</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4184,7 +4184,7 @@
         <v>127153911</v>
       </c>
       <c r="B35" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>127153754</v>
       </c>
       <c r="B36" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>127153801</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127153599</v>
+        <v>127153858</v>
       </c>
       <c r="B38" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,41 +4504,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466439</v>
+        <v>466333</v>
       </c>
       <c r="R38" t="n">
-        <v>6809218</v>
+        <v>6809211</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4598,10 +4594,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127153858</v>
+        <v>127155517</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4636,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466333</v>
+        <v>466108</v>
       </c>
       <c r="R39" t="n">
-        <v>6809211</v>
+        <v>6809230</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,10 +4695,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127155517</v>
+        <v>127153599</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>79052</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4710,37 +4706,41 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466108</v>
+        <v>466439</v>
       </c>
       <c r="R40" t="n">
-        <v>6809230</v>
+        <v>6809218</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4803,7 +4803,7 @@
         <v>127154614</v>
       </c>
       <c r="B41" t="n">
-        <v>80087</v>
+        <v>80089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>127153795</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>127153812</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>127155443</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>127153697</v>
       </c>
       <c r="B45" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127153643</v>
+        <v>127153848</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,42 +1111,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466439</v>
+        <v>466359</v>
       </c>
       <c r="R6" t="n">
-        <v>6809218</v>
+        <v>6809211</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,6 +1182,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1205,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127153848</v>
+        <v>127153643</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,37 +1212,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466359</v>
+        <v>466439</v>
       </c>
       <c r="R7" t="n">
-        <v>6809211</v>
+        <v>6809218</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1288,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -4074,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127153408</v>
+        <v>127153911</v>
       </c>
       <c r="B34" t="n">
-        <v>5177</v>
+        <v>97327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,43 +4085,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466439</v>
+        <v>466299</v>
       </c>
       <c r="R34" t="n">
-        <v>6809218</v>
+        <v>6809206</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4181,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127153911</v>
+        <v>127153408</v>
       </c>
       <c r="B35" t="n">
-        <v>97327</v>
+        <v>5177</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4192,38 +4187,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466299</v>
+        <v>466439</v>
       </c>
       <c r="R35" t="n">
-        <v>6809206</v>
+        <v>6809218</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153754</v>
+        <v>127153801</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,35 +4294,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4330,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466399</v>
+        <v>466383</v>
       </c>
       <c r="R36" t="n">
-        <v>6809202</v>
+        <v>6809213</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,6 +4365,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4392,10 +4384,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153801</v>
+        <v>127153754</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4403,26 +4395,35 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4430,10 +4431,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466383</v>
+        <v>466399</v>
       </c>
       <c r="R37" t="n">
-        <v>6809213</v>
+        <v>6809202</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,7 +4475,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4800,44 +4800,36 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127154614</v>
+        <v>127153795</v>
       </c>
       <c r="B41" t="n">
-        <v>80089</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4846,10 +4838,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466148</v>
+        <v>466388</v>
       </c>
       <c r="R41" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4882,11 +4874,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4914,36 +4901,44 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127153795</v>
+        <v>127154614</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>80089</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4952,10 +4947,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466388</v>
+        <v>466148</v>
       </c>
       <c r="R42" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4988,6 +4983,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -4074,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127153911</v>
+        <v>127153408</v>
       </c>
       <c r="B34" t="n">
-        <v>97327</v>
+        <v>5177</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,38 +4085,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466299</v>
+        <v>466439</v>
       </c>
       <c r="R34" t="n">
-        <v>6809206</v>
+        <v>6809218</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4176,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127153408</v>
+        <v>127153911</v>
       </c>
       <c r="B35" t="n">
-        <v>5177</v>
+        <v>97327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,43 +4192,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466439</v>
+        <v>466299</v>
       </c>
       <c r="R35" t="n">
-        <v>6809218</v>
+        <v>6809206</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127153844</v>
+        <v>127154126</v>
       </c>
       <c r="B2" t="n">
-        <v>80151</v>
+        <v>98471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466359</v>
+        <v>466247</v>
       </c>
       <c r="R2" t="n">
-        <v>6809211</v>
+        <v>6809203</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127154126</v>
+        <v>127153844</v>
       </c>
       <c r="B3" t="n">
-        <v>98471</v>
+        <v>80151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,35 +796,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466247</v>
+        <v>466359</v>
       </c>
       <c r="R3" t="n">
-        <v>6809203</v>
+        <v>6809211</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127155380</v>
+        <v>127154078</v>
       </c>
       <c r="B8" t="n">
         <v>57663</v>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466021</v>
+        <v>466256</v>
       </c>
       <c r="R8" t="n">
-        <v>6809226</v>
+        <v>6809224</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127154078</v>
+        <v>127154595</v>
       </c>
       <c r="B9" t="n">
         <v>57663</v>
@@ -1445,14 +1445,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466256</v>
+        <v>466128</v>
       </c>
       <c r="R9" t="n">
-        <v>6809224</v>
+        <v>6809202</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127154595</v>
+        <v>127155380</v>
       </c>
       <c r="B10" t="n">
         <v>57663</v>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466128</v>
+        <v>466021</v>
       </c>
       <c r="R10" t="n">
-        <v>6809202</v>
+        <v>6809226</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1734,37 +1734,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153712</v>
+        <v>127153879</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>98471</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1772,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466164</v>
+        <v>466321</v>
       </c>
       <c r="R12" t="n">
-        <v>6809202</v>
+        <v>6809223</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,11 +1819,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1828,58 +1832,49 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153879</v>
+        <v>127153712</v>
       </c>
       <c r="B13" t="n">
-        <v>98471</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466321</v>
+        <v>466164</v>
       </c>
       <c r="R13" t="n">
-        <v>6809223</v>
+        <v>6809202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,6 +1920,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1938,12 +1938,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127153899</v>
+        <v>127155499</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>57660</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2809,16 +2809,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2826,7 +2826,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
@@ -2841,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466299</v>
+        <v>466085</v>
       </c>
       <c r="R22" t="n">
-        <v>6809206</v>
+        <v>6809224</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2903,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127155499</v>
+        <v>127153899</v>
       </c>
       <c r="B23" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2914,16 +2918,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2931,11 +2935,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466085</v>
+        <v>466299</v>
       </c>
       <c r="R23" t="n">
-        <v>6809224</v>
+        <v>6809206</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3119,7 +3119,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127154177</v>
+        <v>127154119</v>
       </c>
       <c r="B25" t="n">
         <v>79020</v>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466206</v>
+        <v>466247</v>
       </c>
       <c r="R25" t="n">
-        <v>6809201</v>
+        <v>6809203</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127153768</v>
+        <v>127153920</v>
       </c>
       <c r="B26" t="n">
         <v>79020</v>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466392</v>
+        <v>466298</v>
       </c>
       <c r="R26" t="n">
-        <v>6809204</v>
+        <v>6809205</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,11 +3294,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3326,7 +3321,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127154119</v>
+        <v>127154177</v>
       </c>
       <c r="B27" t="n">
         <v>79020</v>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466247</v>
+        <v>466206</v>
       </c>
       <c r="R27" t="n">
-        <v>6809203</v>
+        <v>6809201</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3427,7 +3422,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127153920</v>
+        <v>127153768</v>
       </c>
       <c r="B28" t="n">
         <v>79020</v>
@@ -3465,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466298</v>
+        <v>466392</v>
       </c>
       <c r="R28" t="n">
-        <v>6809205</v>
+        <v>6809204</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3501,6 +3496,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4493,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127153858</v>
+        <v>127153599</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,37 +4504,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466333</v>
+        <v>466439</v>
       </c>
       <c r="R38" t="n">
-        <v>6809211</v>
+        <v>6809218</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4594,7 +4598,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127155517</v>
+        <v>127153858</v>
       </c>
       <c r="B39" t="n">
         <v>79020</v>
@@ -4632,10 +4636,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466108</v>
+        <v>466333</v>
       </c>
       <c r="R39" t="n">
-        <v>6809230</v>
+        <v>6809211</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4695,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127153599</v>
+        <v>127155517</v>
       </c>
       <c r="B40" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4706,41 +4710,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466439</v>
+        <v>466108</v>
       </c>
       <c r="R40" t="n">
-        <v>6809218</v>
+        <v>6809230</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127154126</v>
       </c>
       <c r="B2" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154078</v>
+        <v>127155380</v>
       </c>
       <c r="B8" t="n">
         <v>57663</v>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466256</v>
+        <v>466021</v>
       </c>
       <c r="R8" t="n">
-        <v>6809224</v>
+        <v>6809226</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127154595</v>
+        <v>127154078</v>
       </c>
       <c r="B9" t="n">
         <v>57663</v>
@@ -1445,14 +1445,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466128</v>
+        <v>466256</v>
       </c>
       <c r="R9" t="n">
-        <v>6809202</v>
+        <v>6809224</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127155380</v>
+        <v>127154595</v>
       </c>
       <c r="B10" t="n">
         <v>57663</v>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466021</v>
+        <v>466128</v>
       </c>
       <c r="R10" t="n">
-        <v>6809226</v>
+        <v>6809202</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153532</v>
+        <v>127153712</v>
       </c>
       <c r="B11" t="n">
         <v>79020</v>
@@ -1667,14 +1667,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466439</v>
+        <v>466164</v>
       </c>
       <c r="R11" t="n">
-        <v>6809218</v>
+        <v>6809202</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1709,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1722,69 +1727,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153879</v>
+        <v>127153532</v>
       </c>
       <c r="B12" t="n">
-        <v>98471</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466321</v>
+        <v>466439</v>
       </c>
       <c r="R12" t="n">
-        <v>6809223</v>
+        <v>6809218</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,37 +1840,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153712</v>
+        <v>127153879</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>98477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466164</v>
+        <v>466321</v>
       </c>
       <c r="R13" t="n">
-        <v>6809202</v>
+        <v>6809223</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,11 +1925,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1938,12 +1938,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1953,7 +1953,7 @@
         <v>127154092</v>
       </c>
       <c r="B14" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155565</v>
+        <v>127155475</v>
       </c>
       <c r="B15" t="n">
         <v>79020</v>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466242</v>
+        <v>466076</v>
       </c>
       <c r="R15" t="n">
-        <v>6809226</v>
+        <v>6809225</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2161,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127153742</v>
+        <v>127155565</v>
       </c>
       <c r="B16" t="n">
         <v>79020</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466410</v>
+        <v>466242</v>
       </c>
       <c r="R16" t="n">
-        <v>6809205</v>
+        <v>6809226</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127155475</v>
+        <v>127153742</v>
       </c>
       <c r="B17" t="n">
         <v>79020</v>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466076</v>
+        <v>466410</v>
       </c>
       <c r="R17" t="n">
-        <v>6809225</v>
+        <v>6809205</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2363,46 +2363,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127154600</v>
+        <v>127154066</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>98477</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466144</v>
+        <v>466274</v>
       </c>
       <c r="R18" t="n">
-        <v>6809220</v>
+        <v>6809202</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,6 +2454,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2472,46 +2473,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127154066</v>
+        <v>127154600</v>
       </c>
       <c r="B19" t="n">
-        <v>98471</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2519,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466274</v>
+        <v>466144</v>
       </c>
       <c r="R19" t="n">
-        <v>6809202</v>
+        <v>6809220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,7 +2564,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>127154181</v>
       </c>
       <c r="B21" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127153920</v>
+        <v>127154177</v>
       </c>
       <c r="B26" t="n">
         <v>79020</v>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466298</v>
+        <v>466206</v>
       </c>
       <c r="R26" t="n">
-        <v>6809205</v>
+        <v>6809201</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127154177</v>
+        <v>127153768</v>
       </c>
       <c r="B27" t="n">
         <v>79020</v>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466206</v>
+        <v>466392</v>
       </c>
       <c r="R27" t="n">
-        <v>6809201</v>
+        <v>6809204</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,6 +3395,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3422,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127153768</v>
+        <v>127153920</v>
       </c>
       <c r="B28" t="n">
         <v>79020</v>
@@ -3460,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466392</v>
+        <v>466298</v>
       </c>
       <c r="R28" t="n">
-        <v>6809204</v>
+        <v>6809205</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3496,11 +3501,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3640,7 +3640,7 @@
         <v>127153894</v>
       </c>
       <c r="B30" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127154630</v>
+        <v>127154111</v>
       </c>
       <c r="B31" t="n">
-        <v>56855</v>
+        <v>57663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3784,7 +3784,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466148</v>
+        <v>466259</v>
       </c>
       <c r="R31" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127154111</v>
+        <v>127155460</v>
       </c>
       <c r="B32" t="n">
         <v>57663</v>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466259</v>
+        <v>466067</v>
       </c>
       <c r="R32" t="n">
-        <v>6809208</v>
+        <v>6809228</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127155460</v>
+        <v>127154630</v>
       </c>
       <c r="B33" t="n">
-        <v>57663</v>
+        <v>56855</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466067</v>
+        <v>466148</v>
       </c>
       <c r="R33" t="n">
-        <v>6809228</v>
+        <v>6809222</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4074,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127153408</v>
+        <v>127153911</v>
       </c>
       <c r="B34" t="n">
-        <v>5177</v>
+        <v>97333</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,43 +4085,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466439</v>
+        <v>466299</v>
       </c>
       <c r="R34" t="n">
-        <v>6809218</v>
+        <v>6809206</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4181,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127153911</v>
+        <v>127153408</v>
       </c>
       <c r="B35" t="n">
-        <v>97327</v>
+        <v>5177</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4192,38 +4187,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466299</v>
+        <v>466439</v>
       </c>
       <c r="R35" t="n">
-        <v>6809206</v>
+        <v>6809218</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153801</v>
+        <v>127153754</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,26 +4294,35 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4321,10 +4330,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466383</v>
+        <v>466399</v>
       </c>
       <c r="R36" t="n">
-        <v>6809213</v>
+        <v>6809202</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,7 +4374,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4384,10 +4392,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153754</v>
+        <v>127153801</v>
       </c>
       <c r="B37" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4395,35 +4403,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4431,10 +4430,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466399</v>
+        <v>466383</v>
       </c>
       <c r="R37" t="n">
-        <v>6809202</v>
+        <v>6809213</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4475,6 +4474,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127153599</v>
+        <v>127153858</v>
       </c>
       <c r="B38" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,41 +4504,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466439</v>
+        <v>466333</v>
       </c>
       <c r="R38" t="n">
-        <v>6809218</v>
+        <v>6809211</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4598,7 +4594,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127153858</v>
+        <v>127155517</v>
       </c>
       <c r="B39" t="n">
         <v>79020</v>
@@ -4636,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466333</v>
+        <v>466108</v>
       </c>
       <c r="R39" t="n">
-        <v>6809211</v>
+        <v>6809230</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,10 +4695,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127155517</v>
+        <v>127153599</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4710,37 +4706,41 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466108</v>
+        <v>466439</v>
       </c>
       <c r="R40" t="n">
-        <v>6809230</v>
+        <v>6809218</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4800,36 +4800,44 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127153795</v>
+        <v>127154614</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>80089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4838,10 +4846,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466388</v>
+        <v>466148</v>
       </c>
       <c r="R41" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4874,6 +4882,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4901,44 +4914,36 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127154614</v>
+        <v>127153795</v>
       </c>
       <c r="B42" t="n">
-        <v>80089</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4947,10 +4952,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466148</v>
+        <v>466388</v>
       </c>
       <c r="R42" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4983,11 +4988,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5015,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127153812</v>
+        <v>127153697</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>91356</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5026,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466380</v>
+        <v>466269</v>
       </c>
       <c r="R43" t="n">
-        <v>6809217</v>
+        <v>6809223</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,6 +5091,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5104,12 +5109,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5217,10 +5222,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127153697</v>
+        <v>127153812</v>
       </c>
       <c r="B45" t="n">
-        <v>91350</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5228,21 +5233,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5255,10 +5260,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466269</v>
+        <v>466380</v>
       </c>
       <c r="R45" t="n">
-        <v>6809223</v>
+        <v>6809217</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5293,11 +5298,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5311,12 +5311,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127154126</v>
+        <v>127153844</v>
       </c>
       <c r="B2" t="n">
-        <v>98477</v>
+        <v>80154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,35 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466247</v>
+        <v>466359</v>
       </c>
       <c r="R2" t="n">
-        <v>6809203</v>
+        <v>6809211</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127153844</v>
+        <v>127154126</v>
       </c>
       <c r="B3" t="n">
-        <v>80151</v>
+        <v>98480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,26 +787,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466359</v>
+        <v>466247</v>
       </c>
       <c r="R3" t="n">
-        <v>6809211</v>
+        <v>6809203</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127153831</v>
+        <v>127155482</v>
       </c>
       <c r="B4" t="n">
-        <v>79052</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,21 +897,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -919,8 +919,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -928,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466371</v>
+        <v>466081</v>
       </c>
       <c r="R4" t="n">
-        <v>6809222</v>
+        <v>6809216</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +977,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -991,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127155482</v>
+        <v>127153831</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>79055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1024,13 +1028,8 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1038,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466081</v>
+        <v>466371</v>
       </c>
       <c r="R5" t="n">
-        <v>6809216</v>
+        <v>6809222</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,6 +1081,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>127153848</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>127153643</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>127155380</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>127154078</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>127154595</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,37 +1633,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153712</v>
+        <v>127153879</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>98480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1671,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466164</v>
+        <v>466321</v>
       </c>
       <c r="R11" t="n">
-        <v>6809202</v>
+        <v>6809223</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,11 +1718,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1727,12 +1731,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1742,7 +1746,7 @@
         <v>127153532</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,46 +1844,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153879</v>
+        <v>127153712</v>
       </c>
       <c r="B13" t="n">
-        <v>98477</v>
+        <v>79023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466321</v>
+        <v>466164</v>
       </c>
       <c r="R13" t="n">
-        <v>6809223</v>
+        <v>6809202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,6 +1920,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1938,12 +1938,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1953,7 +1953,7 @@
         <v>127154092</v>
       </c>
       <c r="B14" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155475</v>
+        <v>127155565</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466076</v>
+        <v>466242</v>
       </c>
       <c r="R15" t="n">
-        <v>6809225</v>
+        <v>6809226</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127155565</v>
+        <v>127153742</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466242</v>
+        <v>466410</v>
       </c>
       <c r="R16" t="n">
-        <v>6809226</v>
+        <v>6809205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127153742</v>
+        <v>127155475</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466410</v>
+        <v>466076</v>
       </c>
       <c r="R17" t="n">
-        <v>6809205</v>
+        <v>6809225</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2363,46 +2363,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127154066</v>
+        <v>127154600</v>
       </c>
       <c r="B18" t="n">
-        <v>98477</v>
+        <v>57666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466274</v>
+        <v>466144</v>
       </c>
       <c r="R18" t="n">
-        <v>6809202</v>
+        <v>6809220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,7 +2454,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2473,46 +2472,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127154600</v>
+        <v>127154066</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>98480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2520,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466144</v>
+        <v>466274</v>
       </c>
       <c r="R19" t="n">
-        <v>6809220</v>
+        <v>6809202</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,6 +2563,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>127153709</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>127154181</v>
       </c>
       <c r="B21" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2798,27 +2798,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127155499</v>
+        <v>127155506</v>
       </c>
       <c r="B22" t="n">
-        <v>57660</v>
+        <v>5197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2826,16 +2826,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2889,6 +2886,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2910,7 +2908,7 @@
         <v>127153899</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3012,27 +3010,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127155506</v>
+        <v>127155499</v>
       </c>
       <c r="B24" t="n">
-        <v>5197</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3040,13 +3038,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3100,7 +3101,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127154119</v>
+        <v>127154177</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466247</v>
+        <v>466206</v>
       </c>
       <c r="R25" t="n">
-        <v>6809203</v>
+        <v>6809201</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,10 +3220,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127154177</v>
+        <v>127153768</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466206</v>
+        <v>466392</v>
       </c>
       <c r="R26" t="n">
-        <v>6809201</v>
+        <v>6809204</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,6 +3294,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3321,10 +3326,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127153768</v>
+        <v>127154119</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466392</v>
+        <v>466247</v>
       </c>
       <c r="R27" t="n">
-        <v>6809204</v>
+        <v>6809203</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,11 +3400,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3430,7 +3430,7 @@
         <v>127153920</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>127154103</v>
       </c>
       <c r="B29" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>127153894</v>
       </c>
       <c r="B30" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127154111</v>
+        <v>127154630</v>
       </c>
       <c r="B31" t="n">
-        <v>57663</v>
+        <v>56858</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3784,7 +3784,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466259</v>
+        <v>466148</v>
       </c>
       <c r="R31" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,10 +3856,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127155460</v>
+        <v>127154111</v>
       </c>
       <c r="B32" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466067</v>
+        <v>466259</v>
       </c>
       <c r="R32" t="n">
-        <v>6809228</v>
+        <v>6809208</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127154630</v>
+        <v>127155460</v>
       </c>
       <c r="B33" t="n">
-        <v>56855</v>
+        <v>57666</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466148</v>
+        <v>466067</v>
       </c>
       <c r="R33" t="n">
-        <v>6809222</v>
+        <v>6809228</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4074,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127153911</v>
+        <v>127153408</v>
       </c>
       <c r="B34" t="n">
-        <v>97333</v>
+        <v>5177</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,38 +4085,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466299</v>
+        <v>466439</v>
       </c>
       <c r="R34" t="n">
-        <v>6809206</v>
+        <v>6809218</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4176,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127153408</v>
+        <v>127153911</v>
       </c>
       <c r="B35" t="n">
-        <v>5177</v>
+        <v>97336</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,43 +4192,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466439</v>
+        <v>466299</v>
       </c>
       <c r="R35" t="n">
-        <v>6809218</v>
+        <v>6809206</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153754</v>
+        <v>127153801</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,35 +4294,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4330,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466399</v>
+        <v>466383</v>
       </c>
       <c r="R36" t="n">
-        <v>6809202</v>
+        <v>6809213</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,6 +4365,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4392,10 +4384,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153801</v>
+        <v>127153754</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4403,26 +4395,35 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4430,10 +4431,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466383</v>
+        <v>466399</v>
       </c>
       <c r="R37" t="n">
-        <v>6809213</v>
+        <v>6809202</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,7 +4475,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>127153858</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>127155517</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>127153599</v>
       </c>
       <c r="B40" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4800,44 +4800,36 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127154614</v>
+        <v>127153795</v>
       </c>
       <c r="B41" t="n">
-        <v>80089</v>
+        <v>79023</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4846,10 +4838,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466148</v>
+        <v>466388</v>
       </c>
       <c r="R41" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4882,11 +4874,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4914,36 +4901,44 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127153795</v>
+        <v>127154614</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>80092</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4952,10 +4947,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466388</v>
+        <v>466148</v>
       </c>
       <c r="R42" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4988,6 +4983,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5015,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127153697</v>
+        <v>127155443</v>
       </c>
       <c r="B43" t="n">
-        <v>91356</v>
+        <v>79023</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5026,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466269</v>
+        <v>466062</v>
       </c>
       <c r="R43" t="n">
-        <v>6809223</v>
+        <v>6809234</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,11 +5091,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5109,22 +5104,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127155443</v>
+        <v>127153697</v>
       </c>
       <c r="B44" t="n">
-        <v>79020</v>
+        <v>91359</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5132,21 +5127,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5159,10 +5154,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466062</v>
+        <v>466269</v>
       </c>
       <c r="R44" t="n">
-        <v>6809234</v>
+        <v>6809223</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5197,6 +5192,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5210,12 +5210,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5225,7 +5225,7 @@
         <v>127153812</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127153844</v>
       </c>
       <c r="B2" t="n">
-        <v>80154</v>
+        <v>80160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127154126</v>
       </c>
       <c r="B3" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127155482</v>
+        <v>127153831</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>79061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,21 +897,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -919,13 +919,8 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466081</v>
+        <v>466371</v>
       </c>
       <c r="R4" t="n">
-        <v>6809216</v>
+        <v>6809222</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,6 +972,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -995,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127153831</v>
+        <v>127155482</v>
       </c>
       <c r="B5" t="n">
-        <v>79055</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1028,8 +1024,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466371</v>
+        <v>466081</v>
       </c>
       <c r="R5" t="n">
-        <v>6809222</v>
+        <v>6809216</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1082,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>127153848</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>127153643</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>127155380</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>127154078</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>127154595</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,46 +1633,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153879</v>
+        <v>127153712</v>
       </c>
       <c r="B11" t="n">
-        <v>98480</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1680,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466321</v>
+        <v>466164</v>
       </c>
       <c r="R11" t="n">
-        <v>6809223</v>
+        <v>6809202</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,6 +1709,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1731,12 +1727,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1746,7 +1742,7 @@
         <v>127153532</v>
       </c>
       <c r="B12" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,37 +1840,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153712</v>
+        <v>127153879</v>
       </c>
       <c r="B13" t="n">
-        <v>79023</v>
+        <v>98488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466164</v>
+        <v>466321</v>
       </c>
       <c r="R13" t="n">
-        <v>6809202</v>
+        <v>6809223</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,11 +1925,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1938,12 +1938,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1953,7 +1953,7 @@
         <v>127154092</v>
       </c>
       <c r="B14" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155565</v>
+        <v>127155475</v>
       </c>
       <c r="B15" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466242</v>
+        <v>466076</v>
       </c>
       <c r="R15" t="n">
-        <v>6809226</v>
+        <v>6809225</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127153742</v>
+        <v>127155565</v>
       </c>
       <c r="B16" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466410</v>
+        <v>466242</v>
       </c>
       <c r="R16" t="n">
-        <v>6809205</v>
+        <v>6809226</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127155475</v>
+        <v>127153742</v>
       </c>
       <c r="B17" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466076</v>
+        <v>466410</v>
       </c>
       <c r="R17" t="n">
-        <v>6809225</v>
+        <v>6809205</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2366,7 +2366,7 @@
         <v>127154600</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>127154066</v>
       </c>
       <c r="B19" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>127153709</v>
       </c>
       <c r="B20" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>127154181</v>
       </c>
       <c r="B21" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2798,27 +2798,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127155506</v>
+        <v>127153899</v>
       </c>
       <c r="B22" t="n">
-        <v>5197</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2827,12 +2827,11 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2842,10 +2841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466085</v>
+        <v>466299</v>
       </c>
       <c r="R22" t="n">
-        <v>6809224</v>
+        <v>6809206</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2886,7 +2885,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2905,27 +2903,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127153899</v>
+        <v>127155506</v>
       </c>
       <c r="B23" t="n">
-        <v>57666</v>
+        <v>5197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2934,11 +2932,12 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2948,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466299</v>
+        <v>466085</v>
       </c>
       <c r="R23" t="n">
-        <v>6809206</v>
+        <v>6809224</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,6 +2991,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>127155499</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127154177</v>
+        <v>127154119</v>
       </c>
       <c r="B25" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466206</v>
+        <v>466247</v>
       </c>
       <c r="R25" t="n">
-        <v>6809201</v>
+        <v>6809203</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,10 +3220,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127153768</v>
+        <v>127154177</v>
       </c>
       <c r="B26" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466392</v>
+        <v>466206</v>
       </c>
       <c r="R26" t="n">
-        <v>6809204</v>
+        <v>6809201</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,11 +3294,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3326,10 +3321,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127154119</v>
+        <v>127153768</v>
       </c>
       <c r="B27" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466247</v>
+        <v>466392</v>
       </c>
       <c r="R27" t="n">
-        <v>6809203</v>
+        <v>6809204</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3400,6 +3395,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3430,7 +3430,7 @@
         <v>127153920</v>
       </c>
       <c r="B28" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>127154103</v>
       </c>
       <c r="B29" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>127153894</v>
       </c>
       <c r="B30" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127154630</v>
+        <v>127154111</v>
       </c>
       <c r="B31" t="n">
-        <v>56858</v>
+        <v>57672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3784,7 +3784,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466148</v>
+        <v>466259</v>
       </c>
       <c r="R31" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,10 +3856,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127154111</v>
+        <v>127155460</v>
       </c>
       <c r="B32" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466259</v>
+        <v>466067</v>
       </c>
       <c r="R32" t="n">
-        <v>6809208</v>
+        <v>6809228</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127155460</v>
+        <v>127154630</v>
       </c>
       <c r="B33" t="n">
-        <v>57666</v>
+        <v>56864</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466067</v>
+        <v>466148</v>
       </c>
       <c r="R33" t="n">
-        <v>6809228</v>
+        <v>6809222</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4184,7 +4184,7 @@
         <v>127153911</v>
       </c>
       <c r="B35" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>127153801</v>
       </c>
       <c r="B36" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>127153754</v>
       </c>
       <c r="B37" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127153858</v>
+        <v>127153599</v>
       </c>
       <c r="B38" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,37 +4504,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466333</v>
+        <v>466439</v>
       </c>
       <c r="R38" t="n">
-        <v>6809211</v>
+        <v>6809218</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4594,10 +4598,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127155517</v>
+        <v>127153858</v>
       </c>
       <c r="B39" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4632,10 +4636,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466108</v>
+        <v>466333</v>
       </c>
       <c r="R39" t="n">
-        <v>6809230</v>
+        <v>6809211</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4695,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127153599</v>
+        <v>127155517</v>
       </c>
       <c r="B40" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4706,41 +4710,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466439</v>
+        <v>466108</v>
       </c>
       <c r="R40" t="n">
-        <v>6809218</v>
+        <v>6809230</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4800,36 +4800,44 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127153795</v>
+        <v>127154614</v>
       </c>
       <c r="B41" t="n">
-        <v>79023</v>
+        <v>80098</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4838,10 +4846,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466388</v>
+        <v>466148</v>
       </c>
       <c r="R41" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4874,6 +4882,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4901,44 +4914,36 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127154614</v>
+        <v>127153795</v>
       </c>
       <c r="B42" t="n">
-        <v>80092</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4947,10 +4952,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466148</v>
+        <v>466388</v>
       </c>
       <c r="R42" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4983,11 +4988,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5015,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127155443</v>
+        <v>127153697</v>
       </c>
       <c r="B43" t="n">
-        <v>79023</v>
+        <v>91367</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5026,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466062</v>
+        <v>466269</v>
       </c>
       <c r="R43" t="n">
-        <v>6809234</v>
+        <v>6809223</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,6 +5091,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5104,22 +5109,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127153697</v>
+        <v>127155443</v>
       </c>
       <c r="B44" t="n">
-        <v>91359</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5127,21 +5132,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5154,10 +5159,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466269</v>
+        <v>466062</v>
       </c>
       <c r="R44" t="n">
-        <v>6809223</v>
+        <v>6809234</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5192,11 +5197,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5210,12 +5210,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5225,7 +5225,7 @@
         <v>127153812</v>
       </c>
       <c r="B45" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127153844</v>
+        <v>127154126</v>
       </c>
       <c r="B2" t="n">
-        <v>80160</v>
+        <v>98489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466359</v>
+        <v>466247</v>
       </c>
       <c r="R2" t="n">
-        <v>6809211</v>
+        <v>6809203</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127154126</v>
+        <v>127153844</v>
       </c>
       <c r="B3" t="n">
-        <v>98488</v>
+        <v>80160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,35 +796,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466247</v>
+        <v>466359</v>
       </c>
       <c r="R3" t="n">
-        <v>6809203</v>
+        <v>6809211</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127153848</v>
+        <v>127153643</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,37 +1111,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466359</v>
+        <v>466439</v>
       </c>
       <c r="R6" t="n">
-        <v>6809211</v>
+        <v>6809218</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1187,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1201,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127153643</v>
+        <v>127153848</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,42 +1216,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466439</v>
+        <v>466359</v>
       </c>
       <c r="R7" t="n">
-        <v>6809218</v>
+        <v>6809211</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,6 +1287,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153712</v>
+        <v>127153532</v>
       </c>
       <c r="B11" t="n">
         <v>79029</v>
@@ -1667,14 +1667,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466164</v>
+        <v>466439</v>
       </c>
       <c r="R11" t="n">
-        <v>6809202</v>
+        <v>6809218</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,11 +1709,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1727,19 +1722,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153532</v>
+        <v>127153712</v>
       </c>
       <c r="B12" t="n">
         <v>79029</v>
@@ -1773,14 +1768,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466439</v>
+        <v>466164</v>
       </c>
       <c r="R12" t="n">
-        <v>6809218</v>
+        <v>6809202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,6 +1810,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1828,12 +1828,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1843,7 +1843,7 @@
         <v>127153879</v>
       </c>
       <c r="B13" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>127154092</v>
       </c>
       <c r="B14" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155475</v>
+        <v>127155565</v>
       </c>
       <c r="B15" t="n">
         <v>79029</v>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466076</v>
+        <v>466242</v>
       </c>
       <c r="R15" t="n">
-        <v>6809225</v>
+        <v>6809226</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2161,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127155565</v>
+        <v>127153742</v>
       </c>
       <c r="B16" t="n">
         <v>79029</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466242</v>
+        <v>466410</v>
       </c>
       <c r="R16" t="n">
-        <v>6809226</v>
+        <v>6809205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127153742</v>
+        <v>127155475</v>
       </c>
       <c r="B17" t="n">
         <v>79029</v>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466410</v>
+        <v>466076</v>
       </c>
       <c r="R17" t="n">
-        <v>6809205</v>
+        <v>6809225</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
         <v>127154066</v>
       </c>
       <c r="B19" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,46 +2582,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127153709</v>
+        <v>127154181</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>98385</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2629,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466410</v>
+        <v>466206</v>
       </c>
       <c r="R20" t="n">
-        <v>6809209</v>
+        <v>6809201</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,17 +2659,13 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2696,38 +2684,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127154181</v>
+        <v>127153709</v>
       </c>
       <c r="B21" t="n">
-        <v>98384</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2735,10 +2731,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466206</v>
+        <v>466410</v>
       </c>
       <c r="R21" t="n">
-        <v>6809201</v>
+        <v>6809209</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,13 +2769,17 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2798,10 +2798,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127153899</v>
+        <v>127155499</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>57669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2809,16 +2809,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2826,7 +2826,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
@@ -2841,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466299</v>
+        <v>466085</v>
       </c>
       <c r="R22" t="n">
-        <v>6809206</v>
+        <v>6809224</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2903,27 +2907,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127155506</v>
+        <v>127153899</v>
       </c>
       <c r="B23" t="n">
-        <v>5197</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2932,12 +2936,11 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2947,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466085</v>
+        <v>466299</v>
       </c>
       <c r="R23" t="n">
-        <v>6809224</v>
+        <v>6809206</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2991,7 +2994,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3010,27 +3012,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127155499</v>
+        <v>127155506</v>
       </c>
       <c r="B24" t="n">
-        <v>57669</v>
+        <v>5197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3038,16 +3040,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3101,6 +3100,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3119,7 +3119,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127154119</v>
+        <v>127154177</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466247</v>
+        <v>466206</v>
       </c>
       <c r="R25" t="n">
-        <v>6809203</v>
+        <v>6809201</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127154177</v>
+        <v>127153768</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466206</v>
+        <v>466392</v>
       </c>
       <c r="R26" t="n">
-        <v>6809201</v>
+        <v>6809204</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,6 +3294,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3321,7 +3326,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127153768</v>
+        <v>127154119</v>
       </c>
       <c r="B27" t="n">
         <v>79029</v>
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466392</v>
+        <v>466247</v>
       </c>
       <c r="R27" t="n">
-        <v>6809204</v>
+        <v>6809203</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,11 +3400,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3640,7 +3640,7 @@
         <v>127153894</v>
       </c>
       <c r="B30" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>127153911</v>
       </c>
       <c r="B35" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153801</v>
+        <v>127153754</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,26 +4294,35 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4321,10 +4330,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466383</v>
+        <v>466399</v>
       </c>
       <c r="R36" t="n">
-        <v>6809213</v>
+        <v>6809202</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,7 +4374,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4384,10 +4392,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153754</v>
+        <v>127153801</v>
       </c>
       <c r="B37" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4395,35 +4403,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4431,10 +4430,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466399</v>
+        <v>466383</v>
       </c>
       <c r="R37" t="n">
-        <v>6809202</v>
+        <v>6809213</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4475,6 +4474,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5015,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127153697</v>
+        <v>127153812</v>
       </c>
       <c r="B43" t="n">
-        <v>91367</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5026,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466269</v>
+        <v>466380</v>
       </c>
       <c r="R43" t="n">
-        <v>6809223</v>
+        <v>6809217</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,11 +5091,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5109,12 +5104,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5222,10 +5217,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127153812</v>
+        <v>127153697</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>91368</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5233,21 +5228,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5260,10 +5255,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466380</v>
+        <v>466269</v>
       </c>
       <c r="R45" t="n">
-        <v>6809217</v>
+        <v>6809223</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5298,6 +5293,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5311,12 +5311,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127154126</v>
+        <v>127153844</v>
       </c>
       <c r="B2" t="n">
-        <v>98489</v>
+        <v>80142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,35 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466247</v>
+        <v>466359</v>
       </c>
       <c r="R2" t="n">
-        <v>6809203</v>
+        <v>6809211</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127153844</v>
+        <v>127154126</v>
       </c>
       <c r="B3" t="n">
-        <v>80160</v>
+        <v>98457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,26 +787,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466359</v>
+        <v>466247</v>
       </c>
       <c r="R3" t="n">
-        <v>6809211</v>
+        <v>6809203</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
         <v>127153831</v>
       </c>
       <c r="B4" t="n">
-        <v>79061</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127155482</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>127153643</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127153848</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>127155380</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>127154078</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>127154595</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1636,7 +1636,7 @@
         <v>127153532</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>127153712</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>127153879</v>
       </c>
       <c r="B13" t="n">
-        <v>98489</v>
+        <v>98457</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>127154092</v>
       </c>
       <c r="B14" t="n">
-        <v>98489</v>
+        <v>98457</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>127155565</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>127153742</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>127155475</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2363,46 +2363,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127154600</v>
+        <v>127154066</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>98457</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466144</v>
+        <v>466274</v>
       </c>
       <c r="R18" t="n">
-        <v>6809220</v>
+        <v>6809202</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,6 +2454,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2472,46 +2473,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127154066</v>
+        <v>127154600</v>
       </c>
       <c r="B19" t="n">
-        <v>98489</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2519,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466274</v>
+        <v>466144</v>
       </c>
       <c r="R19" t="n">
-        <v>6809202</v>
+        <v>6809220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,7 +2564,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2575,45 +2575,53 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127154181</v>
+        <v>127153709</v>
       </c>
       <c r="B20" t="n">
-        <v>98385</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2621,10 +2629,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466206</v>
+        <v>466410</v>
       </c>
       <c r="R20" t="n">
-        <v>6809201</v>
+        <v>6809209</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,13 +2667,17 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2684,46 +2696,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127153709</v>
+        <v>127154181</v>
       </c>
       <c r="B21" t="n">
-        <v>57672</v>
+        <v>98353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2731,10 +2735,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466410</v>
+        <v>466206</v>
       </c>
       <c r="R21" t="n">
-        <v>6809209</v>
+        <v>6809201</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,17 +2773,13 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2801,7 +2801,7 @@
         <v>127155499</v>
       </c>
       <c r="B22" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>127153899</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>127155506</v>
       </c>
       <c r="B24" t="n">
-        <v>5197</v>
+        <v>5196</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>127154177</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>127153768</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>127154119</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>127153920</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3528,46 +3528,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127154103</v>
+        <v>127153894</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>98457</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466254</v>
+        <v>466299</v>
       </c>
       <c r="R29" t="n">
-        <v>6809208</v>
+        <v>6809206</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3619,6 +3619,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3637,46 +3638,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127153894</v>
+        <v>127154103</v>
       </c>
       <c r="B30" t="n">
-        <v>98489</v>
+        <v>57657</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3684,10 +3685,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466299</v>
+        <v>466254</v>
       </c>
       <c r="R30" t="n">
-        <v>6809206</v>
+        <v>6809208</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3728,7 +3729,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>127154111</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>127155460</v>
       </c>
       <c r="B32" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>127154630</v>
       </c>
       <c r="B33" t="n">
-        <v>56864</v>
+        <v>56849</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4077,7 +4077,7 @@
         <v>127153408</v>
       </c>
       <c r="B34" t="n">
-        <v>5177</v>
+        <v>5176</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>127153911</v>
       </c>
       <c r="B35" t="n">
-        <v>97345</v>
+        <v>97314</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153754</v>
+        <v>127153801</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>79011</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,35 +4294,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4330,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466399</v>
+        <v>466383</v>
       </c>
       <c r="R36" t="n">
-        <v>6809202</v>
+        <v>6809213</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,6 +4365,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4392,10 +4384,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153801</v>
+        <v>127153754</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4403,26 +4395,35 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4430,10 +4431,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466383</v>
+        <v>466399</v>
       </c>
       <c r="R37" t="n">
-        <v>6809213</v>
+        <v>6809202</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,7 +4475,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>127153599</v>
       </c>
       <c r="B38" t="n">
-        <v>79061</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>127153858</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>127155517</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4800,44 +4800,36 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127154614</v>
+        <v>127153795</v>
       </c>
       <c r="B41" t="n">
-        <v>80098</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4846,10 +4838,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466148</v>
+        <v>466388</v>
       </c>
       <c r="R41" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4882,11 +4874,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4914,36 +4901,44 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127153795</v>
+        <v>127154614</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>80080</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4952,10 +4947,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466388</v>
+        <v>466148</v>
       </c>
       <c r="R42" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4988,6 +4983,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5018,7 +5018,7 @@
         <v>127153812</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>127155443</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>127153697</v>
       </c>
       <c r="B45" t="n">
-        <v>91368</v>
+        <v>91337</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,46 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127154126</v>
+        <v>127156923</v>
       </c>
       <c r="B2" t="n">
-        <v>98489</v>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466247</v>
+        <v>466105</v>
       </c>
       <c r="R2" t="n">
-        <v>6809203</v>
+        <v>6809241</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,6 +749,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På en granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,22 +769,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127153844</v>
+        <v>127153657</v>
       </c>
       <c r="B3" t="n">
-        <v>80160</v>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466359</v>
+        <v>466280</v>
       </c>
       <c r="R3" t="n">
-        <v>6809211</v>
+        <v>6809230</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,6 +857,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -874,51 +875,47 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127153831</v>
+        <v>127153668</v>
       </c>
       <c r="B4" t="n">
-        <v>79061</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -928,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466371</v>
+        <v>466206</v>
       </c>
       <c r="R4" t="n">
-        <v>6809222</v>
+        <v>6809201</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,46 +988,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127155482</v>
+        <v>127153712</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1038,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466081</v>
+        <v>466164</v>
       </c>
       <c r="R5" t="n">
-        <v>6809216</v>
+        <v>6809202</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,77 +1064,78 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127153643</v>
+        <v>127154119</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466439</v>
+        <v>466247</v>
       </c>
       <c r="R6" t="n">
-        <v>6809218</v>
+        <v>6809203</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,6 +1176,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1205,14 +1195,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127153848</v>
+        <v>127154208</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1243,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466359</v>
+        <v>466190</v>
       </c>
       <c r="R7" t="n">
-        <v>6809211</v>
+        <v>6809189</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,46 +1296,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127155380</v>
+        <v>127154246</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1353,10 +1334,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466021</v>
+        <v>466177</v>
       </c>
       <c r="R8" t="n">
-        <v>6809226</v>
+        <v>6809177</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,6 +1378,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1415,46 +1397,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127154078</v>
+        <v>127155066</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1462,10 +1435,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466256</v>
+        <v>466046</v>
       </c>
       <c r="R9" t="n">
-        <v>6809224</v>
+        <v>6809186</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,6 +1479,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1524,46 +1498,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127154595</v>
+        <v>127155443</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1571,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466128</v>
+        <v>466062</v>
       </c>
       <c r="R10" t="n">
-        <v>6809202</v>
+        <v>6809234</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,6 +1580,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1633,14 +1599,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153532</v>
+        <v>127155475</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1667,14 +1633,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466439</v>
+        <v>466076</v>
       </c>
       <c r="R11" t="n">
-        <v>6809218</v>
+        <v>6809225</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,14 +1700,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153712</v>
+        <v>127155517</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1772,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466164</v>
+        <v>466108</v>
       </c>
       <c r="R12" t="n">
-        <v>6809202</v>
+        <v>6809230</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,11 +1776,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1828,58 +1789,49 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153879</v>
+        <v>127155525</v>
       </c>
       <c r="B13" t="n">
-        <v>98489</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1887,10 +1839,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466321</v>
+        <v>466136</v>
       </c>
       <c r="R13" t="n">
-        <v>6809223</v>
+        <v>6809240</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,46 +1902,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127154092</v>
+        <v>127155539</v>
       </c>
       <c r="B14" t="n">
-        <v>98489</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1997,10 +1940,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466255</v>
+        <v>466138</v>
       </c>
       <c r="R14" t="n">
-        <v>6809216</v>
+        <v>6809240</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,14 +2003,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155565</v>
+        <v>127155545</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2098,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466242</v>
+        <v>466193</v>
       </c>
       <c r="R15" t="n">
-        <v>6809226</v>
+        <v>6809243</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,14 +2104,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127153742</v>
+        <v>127155553</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2199,10 +2142,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466410</v>
+        <v>466235</v>
       </c>
       <c r="R16" t="n">
-        <v>6809205</v>
+        <v>6809253</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,14 +2205,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127155475</v>
+        <v>127155565</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2300,10 +2243,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466076</v>
+        <v>466242</v>
       </c>
       <c r="R17" t="n">
-        <v>6809225</v>
+        <v>6809226</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2363,27 +2306,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127154600</v>
+        <v>127155499</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2393,14 +2336,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2410,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466144</v>
+        <v>466085</v>
       </c>
       <c r="R18" t="n">
-        <v>6809220</v>
+        <v>6809224</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,10 +2415,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127154066</v>
+        <v>127155573</v>
       </c>
       <c r="B19" t="n">
-        <v>98489</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,35 +2426,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2519,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466274</v>
+        <v>466290</v>
       </c>
       <c r="R19" t="n">
-        <v>6809202</v>
+        <v>6809237</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,7 +2502,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2582,38 +2520,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127154181</v>
+        <v>127154078</v>
       </c>
       <c r="B20" t="n">
-        <v>98385</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2621,10 +2567,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466206</v>
+        <v>466256</v>
       </c>
       <c r="R20" t="n">
-        <v>6809201</v>
+        <v>6809224</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2665,7 +2611,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2684,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127153709</v>
+        <v>127154103</v>
       </c>
       <c r="B21" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2721,7 +2666,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2731,10 +2676,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466410</v>
+        <v>466254</v>
       </c>
       <c r="R21" t="n">
-        <v>6809209</v>
+        <v>6809208</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2767,11 +2712,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2798,10 +2738,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127155499</v>
+        <v>127154111</v>
       </c>
       <c r="B22" t="n">
-        <v>57669</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2809,16 +2749,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2828,7 +2768,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2845,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466085</v>
+        <v>466259</v>
       </c>
       <c r="R22" t="n">
-        <v>6809224</v>
+        <v>6809208</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127153899</v>
+        <v>127154201</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2935,7 +2875,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
@@ -2950,10 +2894,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466299</v>
+        <v>466193</v>
       </c>
       <c r="R23" t="n">
-        <v>6809206</v>
+        <v>6809194</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,27 +2956,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127155506</v>
+        <v>127154206</v>
       </c>
       <c r="B24" t="n">
-        <v>5197</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3040,13 +2984,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3056,10 +3003,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466085</v>
+        <v>466190</v>
       </c>
       <c r="R24" t="n">
-        <v>6809224</v>
+        <v>6809189</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3100,7 +3047,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3119,10 +3065,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127154177</v>
+        <v>127154595</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3130,26 +3076,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3157,10 +3112,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466206</v>
+        <v>466128</v>
       </c>
       <c r="R25" t="n">
-        <v>6809201</v>
+        <v>6809202</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,7 +3156,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3220,10 +3174,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127153768</v>
+        <v>127154600</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3231,26 +3185,35 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3258,10 +3221,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466392</v>
+        <v>466144</v>
       </c>
       <c r="R26" t="n">
-        <v>6809204</v>
+        <v>6809220</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3296,18 +3259,12 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>rikl</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3326,10 +3283,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127154119</v>
+        <v>127155126</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3337,26 +3294,35 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3364,10 +3330,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466247</v>
+        <v>466040</v>
       </c>
       <c r="R27" t="n">
-        <v>6809203</v>
+        <v>6809191</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,7 +3374,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3427,10 +3392,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127153920</v>
+        <v>127155380</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3438,26 +3403,35 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3465,10 +3439,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466298</v>
+        <v>466021</v>
       </c>
       <c r="R28" t="n">
-        <v>6809205</v>
+        <v>6809226</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3509,7 +3483,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3528,10 +3501,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127154103</v>
+        <v>127155460</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3558,7 +3531,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -3575,10 +3548,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466254</v>
+        <v>466067</v>
       </c>
       <c r="R29" t="n">
-        <v>6809208</v>
+        <v>6809228</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3637,46 +3610,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127153894</v>
+        <v>127155482</v>
       </c>
       <c r="B30" t="n">
-        <v>98489</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3684,10 +3657,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466299</v>
+        <v>466081</v>
       </c>
       <c r="R30" t="n">
-        <v>6809206</v>
+        <v>6809216</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3728,7 +3701,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3747,32 +3719,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127154111</v>
+        <v>127154630</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>57141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3784,7 +3756,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3794,10 +3766,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466259</v>
+        <v>466148</v>
       </c>
       <c r="R31" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,27 +3828,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127155460</v>
+        <v>127155506</v>
       </c>
       <c r="B32" t="n">
-        <v>57672</v>
+        <v>5199</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3884,16 +3856,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3903,10 +3872,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466067</v>
+        <v>466085</v>
       </c>
       <c r="R32" t="n">
-        <v>6809228</v>
+        <v>6809224</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3947,6 +3916,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3965,10 +3935,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127154630</v>
+        <v>127155559</v>
       </c>
       <c r="B33" t="n">
-        <v>56864</v>
+        <v>5199</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3976,33 +3946,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +3979,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466148</v>
+        <v>466236</v>
       </c>
       <c r="R33" t="n">
-        <v>6809222</v>
+        <v>6809254</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4056,6 +4023,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4074,10 +4042,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127153408</v>
+        <v>127154181</v>
       </c>
       <c r="B34" t="n">
-        <v>5177</v>
+        <v>99035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,43 +4053,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466439</v>
+        <v>466206</v>
       </c>
       <c r="R34" t="n">
-        <v>6809218</v>
+        <v>6809201</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4181,10 +4144,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127153911</v>
+        <v>127154066</v>
       </c>
       <c r="B35" t="n">
-        <v>97345</v>
+        <v>99140</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4192,26 +4155,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
@@ -4220,10 +4191,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466299</v>
+        <v>466274</v>
       </c>
       <c r="R35" t="n">
-        <v>6809206</v>
+        <v>6809202</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,32 +4254,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153754</v>
+        <v>127154092</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>99140</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4316,13 +4287,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4330,10 +4301,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466399</v>
+        <v>466255</v>
       </c>
       <c r="R36" t="n">
-        <v>6809202</v>
+        <v>6809216</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,6 +4345,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4392,37 +4364,46 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153801</v>
+        <v>127154126</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>99140</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4430,10 +4411,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466383</v>
+        <v>466247</v>
       </c>
       <c r="R37" t="n">
-        <v>6809213</v>
+        <v>6809203</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4493,32 +4474,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127153599</v>
+        <v>127154139</v>
       </c>
       <c r="B38" t="n">
-        <v>79061</v>
+        <v>99140</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4527,18 +4508,23 @@
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466439</v>
+        <v>466238</v>
       </c>
       <c r="R38" t="n">
-        <v>6809218</v>
+        <v>6809238</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4598,36 +4584,44 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127153858</v>
+        <v>127154614</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>80398</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
@@ -4636,10 +4630,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466333</v>
+        <v>466148</v>
       </c>
       <c r="R39" t="n">
-        <v>6809211</v>
+        <v>6809222</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4672,6 +4666,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4699,10 +4698,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127155517</v>
+        <v>127153599</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>79359</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4710,37 +4709,41 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466108</v>
+        <v>466439</v>
       </c>
       <c r="R40" t="n">
-        <v>6809230</v>
+        <v>6809218</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4800,44 +4803,36 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127154614</v>
+        <v>127153634</v>
       </c>
       <c r="B41" t="n">
-        <v>80098</v>
+        <v>79359</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229748</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4846,10 +4841,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466148</v>
+        <v>466339</v>
       </c>
       <c r="R41" t="n">
-        <v>6809222</v>
+        <v>6809232</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4881,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>sälg intill bäck</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4902,22 +4897,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127153795</v>
+        <v>127153831</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>79359</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4925,24 +4920,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -4952,10 +4951,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466388</v>
+        <v>466371</v>
       </c>
       <c r="R42" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5015,14 +5014,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127153812</v>
+        <v>127153340</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5049,14 +5048,14 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466380</v>
+        <v>466439</v>
       </c>
       <c r="R43" t="n">
-        <v>6809217</v>
+        <v>6809218</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5116,14 +5115,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127155443</v>
+        <v>127153742</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5154,10 +5153,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466062</v>
+        <v>466410</v>
       </c>
       <c r="R44" t="n">
-        <v>6809234</v>
+        <v>6809205</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5217,32 +5216,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127153697</v>
+        <v>127153768</v>
       </c>
       <c r="B45" t="n">
-        <v>91368</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5255,10 +5254,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466269</v>
+        <v>466392</v>
       </c>
       <c r="R45" t="n">
-        <v>6809223</v>
+        <v>6809204</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5295,7 +5294,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På en högstubbe</t>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5311,15 +5310,2011 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127153795</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>466388</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6809208</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127153801</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>466383</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6809213</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127153812</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>466380</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6809217</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127153848</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>466359</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6809211</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127153858</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>466333</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6809211</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127153920</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>466298</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6809205</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127155596</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>466299</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6809240</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127153844</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>466359</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6809211</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127153643</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Norr Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>466439</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6809218</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127153709</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>466410</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6809209</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127153754</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>466399</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6809202</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127153825</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>466382</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6809226</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127153899</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>466299</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6809206</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127153408</v>
+      </c>
+      <c r="B59" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Norr Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>466439</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6809218</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127155585</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>466295</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6809241</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127153911</v>
+      </c>
+      <c r="B61" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>466299</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6809206</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127153879</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>466321</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6809223</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127153894</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>466299</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6809206</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127155601</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>466299</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6809240</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31137-2025 artfynd.xlsx
+++ b/artfynd/A 31137-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153599</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153634</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153831</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127156923</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,6 +1225,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153657</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153340</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153668</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153712</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1609,6 +1654,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153742</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1715,6 +1765,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153768</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1816,6 +1871,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153795</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1917,6 +1977,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153801</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2018,6 +2083,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153812</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2119,6 +2189,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153848</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2220,6 +2295,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153858</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2321,6 +2401,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153920</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2422,6 +2507,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154119</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2523,6 +2613,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154208</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2624,6 +2719,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154246</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2725,6 +2825,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155066</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2826,6 +2931,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155443</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2927,6 +3037,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155475</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3028,6 +3143,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155517</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3129,6 +3249,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155525</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3230,6 +3355,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155539</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3331,6 +3461,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155545</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3432,6 +3567,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155553</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3533,6 +3673,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155565</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3634,6 +3779,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155596</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3735,6 +3885,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153844</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3844,6 +3999,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155499</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3949,6 +4109,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155573</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4054,6 +4219,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153643</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4168,6 +4338,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153709</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4277,6 +4452,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153754</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4391,6 +4571,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153825</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4496,6 +4681,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153899</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4605,6 +4795,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154078</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4714,6 +4909,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154103</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4823,6 +5023,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154111</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4932,6 +5137,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154201</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5041,6 +5251,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154206</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5150,6 +5365,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154595</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5259,6 +5479,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154600</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5368,6 +5593,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155126</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5477,6 +5707,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155380</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5586,6 +5821,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155460</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5695,6 +5935,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155482</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5804,6 +6049,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154630</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5911,6 +6161,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153408</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6018,6 +6273,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155506</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6125,6 +6385,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155559</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6227,6 +6492,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154181</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6329,6 +6599,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155585</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6431,6 +6706,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153911</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6541,6 +6821,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153879</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6651,6 +6936,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153894</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6761,6 +7051,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154066</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6871,6 +7166,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154092</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6981,6 +7281,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154126</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7091,6 +7396,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154139</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7201,6 +7511,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155601</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7315,8 +7630,78 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154614</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>